--- a/output/inuts/testcases/inuts_test_plan.xlsx
+++ b/output/inuts/testcases/inuts_test_plan.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Warranty Information Management</t>
+          <t>Usage Display and Breakdown</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Verify Warranty Information Display</t>
+          <t>Verify Data, Voice, SMS, and LD Usages Display</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view their device warranty information</t>
+          <t>Verify that the user is able to view their data, voice, SMS, and LD usages</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -623,35 +623,25 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>User has a valid account and is logged in, ESIDE integration is available</t>
+          <t>User has a valid account with usage data</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Subscriber page
-2. Step 2: Click on the Device Information page area within BBSSC
-3. Step 3: Verify the Warranty expiration date is displayed
-4. Step 4: Verify the Warranty expiration date corresponds to the date of activation
-5. Step 5: Verify the standard manufacturer warranty expiration details of the device are displayed
-6. Step 6: Verify all OEM devices are included for warranty information
-7. Step 7: Enter a valid device serial number in the search field
-8. Step 8: Click the Search button
-9. Step 9: Verify the warranty information for the searched device is displayed
-10. Step 10: Verify the warranty expiration date is displayed in the correct format (MM/DD/YYYY)
-11. Step 11: Verify the user can view the warranty information without any errors
-12. Step 12: Verify the user can navigate back to the Subscriber page without any issues
-13. Step 13: Log out of the application
-14. Step 14: Verify the user is logged out successfully</t>
+          <t>1. Verify Data usage is displayed
+2. Verify Voice usage is displayed
+3. Verify SMS usage is displayed
+4. Verify LD usage is displayed</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>The user is able to view their device warranty information, including the warranty expiration date and standard manufacturer warranty expiration details</t>
+          <t>All usage types are displayed correctly</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Valid device serial number, valid account credentials</t>
+          <t>Sample usage data for data, voice, SMS, and LD</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -668,7 +658,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Warranty Information Management</t>
+          <t>Usage Display and Breakdown</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -678,12 +668,12 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Verify Warranty Information for Invalid Device</t>
+          <t>Verify Breakdown of Roaming, Overage, and In-plan Usages</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to view warranty information for an invalid device</t>
+          <t>Verify that the user is able to view the breakdown of roaming, overage, and in-plan usages</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -703,30 +693,24 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>User has a valid account and is logged in, ESIDE integration is available</t>
+          <t>User has a valid account with usage data</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Subscriber page
-2. Step 2: Click on the Device Information page area within BBSSC
-3. Step 3: Enter an invalid device serial number in the search field
-4. Step 4: Click the Search button
-5. Step 5: Verify an error message is displayed indicating that the device is not found
-6. Step 6: Verify the user is unable to view warranty information for the invalid device
-7. Step 7: Verify the user can navigate back to the Subscriber page without any issues
-8. Step 8: Log out of the application
-9. Step 9: Verify the user is logged out successfully</t>
+          <t>1. Verify Roaming usage breakdown is displayed
+2. Verify Overage usage breakdown is displayed
+3. Verify In-plan usage breakdown is displayed</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>The user is unable to view warranty information for an invalid device and an error message is displayed</t>
+          <t>All usage breakdowns are displayed correctly</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>Invalid device serial number, valid account credentials</t>
+          <t>Sample usage data for roaming, overage, and in-plan</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
@@ -743,7 +727,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Warranty Information Management</t>
+          <t>Usage Display and Breakdown</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -753,12 +737,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Verify Warranty Information for Multiple Devices</t>
+          <t>Verify Error Handling for Empty Usage Data</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view warranty information for multiple devices</t>
+          <t>Verify that the system handles empty usage data correctly</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -778,30 +762,25 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>User has a valid account and is logged in, ESIDE integration is available, multiple devices are associated with the user's account</t>
+          <t>User has a valid account with no usage data</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Subscriber page
-2. Step 2: Click on the Device Information page area within BBSSC
-3. Step 3: Verify the warranty information for each device is displayed
-4. Step 4: Verify the warranty expiration date for each device corresponds to the date of activation
-5. Step 5: Verify the standard manufacturer warranty expiration details for each device are displayed
-6. Step 6: Verify the user can view the warranty information for each device without any errors
-7. Step 7: Verify the user can navigate back to the Subscriber page without any issues
-8. Step 8: Log out of the application
-9. Step 9: Verify the user is logged out successfully</t>
+          <t>1. Verify error message is displayed for empty data usage
+2. Verify error message is displayed for empty voice usage
+3. Verify error message is displayed for empty SMS usage
+4. Verify error message is displayed for empty LD usage</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>The user is able to view warranty information for multiple devices, including the warranty expiration date and standard manufacturer warranty expiration details</t>
+          <t>Error messages are displayed correctly for empty usage data</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Multiple valid device serial numbers, valid account credentials</t>
+          <t>No usage data</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -818,7 +797,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Dashboard Integration</t>
+          <t>Dashboard and Metrics</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -828,12 +807,12 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Dashboard Load Test</t>
+          <t>Verify Dashboard Displays Key Wireless Management Insights and Actions</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view key metrics and usage summary on the dashboard</t>
+          <t>Verify that the user is able to view key wireless management insights and actions on the dashboard</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -853,31 +832,24 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>User has valid login credentials and Kafka and Analance integrations are available</t>
+          <t>User has access to the dashboard</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter 'john.doe@company.com' in the 'Email' field
-3. Enter 'password123' in the 'Password' field
-4. Click the 'Sign In' button
-5. Verify the dashboard loads with key metrics
-6. Verify the key metrics include 'Number of active subscribers', 'Number of Suspended subscribers', and 'Number of Cancelled Subscribers'
-7. Verify the total number of BANS and groups are displayed
-8. Verify the usage summary is available and can toggle between 'data', 'voice', 'long distance', and 'text messaging'
-9. Toggle between each type of usage and verify the correct data is displayed
-10. Verify plans in overage by thresholds (100%, 85%, 75%, &lt;75%) are displayed</t>
+          <t>1. Verify the dashboard displays key wireless management insights and actions
+2. Verify the dashboard displays subscriber metrics
+3. Verify the dashboard displays BANS and groups metrics</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>The user is able to view key metrics and usage summary on the dashboard</t>
+          <t>The dashboard displays key wireless management insights and actions, including subscriber metrics and BANS and groups metrics</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>john.doe@company.com, password123</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -894,7 +866,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Dashboard Integration</t>
+          <t>Dashboard and Metrics</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -904,12 +876,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Usage Summary Toggle Test</t>
+          <t>Verify Metric Tiles Display Accurate Data</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to toggle between each type of usage</t>
+          <t>Verify that the metric tiles display accurate data based on NAG in context</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -929,32 +901,24 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>User has valid login credentials and Kafka and Analance integrations are available</t>
+          <t>User has access to the dashboard and NAG is in context</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter 'john.doe@company.com' in the 'Email' field
-3. Enter 'password123' in the 'Password' field
-4. Click the 'Sign In' button
-5. Verify the dashboard loads with key metrics
-6. Click on the 'Usage at a glance' section
-7. Verify the usage summary is available and can toggle between 'data', 'voice', 'long distance', and 'text messaging'
-8. Toggle to 'data' and verify the correct data is displayed
-9. Toggle to 'voice' and verify the correct data is displayed
-10. Toggle to 'long distance' and verify the correct data is displayed
-11. Toggle to 'text messaging' and verify the correct data is displayed</t>
+          <t>1. Verify the metric tiles display accurate data for each type (Groups, Billing Accounts, Active, Suspended and Canceled subscribers)
+2. Verify the metric tiles link to the correct view within BBSSC upon selection
+3. Verify the Canceled subscribers tile displays data for the past 30 days</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>The user is able to toggle between each type of usage and view the correct data</t>
+          <t>The metric tiles display accurate data and link to the correct view within BBSSC</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>john.doe@company.com, password123</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -971,7 +935,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Dashboard Integration</t>
+          <t>Dashboard and Metrics</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -981,12 +945,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Dashboard Load Test with Invalid Credentials</t>
+          <t>Verify Usage Summary Tabs Display Correct Data</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to view the dashboard with invalid login credentials</t>
+          <t>Verify that the usage summary tabs display the correct data based on the selected grouping</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -1006,26 +970,24 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>User has invalid login credentials</t>
+          <t>User has access to the dashboard</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter 'invalid.email@company.com' in the 'Email' field
-3. Enter 'invalidpassword' in the 'Password' field
-4. Click the 'Sign In' button
-5. Verify an error message is displayed indicating invalid credentials</t>
+          <t>1. Verify the 'Data' grouping is the default view upon login
+2. Verify selecting a different grouping (Voice, Long Distance, SMS) displays the correct data
+3. Verify the selected grouping persists across reloads</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>The user is unable to view the dashboard and an error message is displayed</t>
+          <t>The usage summary tabs display the correct data based on the selected grouping</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>invalid.email@company.com, invalidpassword</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
@@ -1042,7 +1004,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Detailed Table for Plans and Subscribers</t>
+          <t>Order and Shopping Management</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1052,12 +1014,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Selection of Shareplan group brings customer to separate table with listed details</t>
+          <t>Display Latest Orders</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view a detailed breakdown of their plans and subscribers after selecting a Shareplan group</t>
+          <t>Verify that the system displays the latest orders</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1070,37 +1032,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>The customer has multiple Shareplan groups and the user has the necessary permissions to view the Shareplans Detail Table</t>
+          <t>User has placed at least one order</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Usage Drilldown Table page
-2. Select a Shareplan group corresponding to the Data Usage Type (In-plan, Roaming and Overage)
-3. Click on the selected Shareplan group to view the detailed table
-4. Verify that the detailed table is displayed with the listed details: Billing account, Plan Name, # of subscribers, Allowance (MB), Used (MB), and Overage (MB)
-5. Verify that the data is sorted based on the billing account's alphabetical order
-6. Verify that the data is accurately representing the correct allowance, used, and overage
-7. Verify that the Plan name grouping data is accurate and displays appropriate information according to the Billing Account Number (BAN)
-8. Verify that the columns display numerical values in MB for allowance, used data, and overage within the same row
-9. Verify that the Back Button is implemented to bring the user back to the standard Usage Bar Chart Drilldown View</t>
+          <t>1. Navigate to the Shopping and Orders Widget
+2. Verify the Latest Orders Table is displayed
+3. Verify the latest orders are listed in the Latest Orders Table</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>The user is able to view a detailed breakdown of their plans and subscribers after selecting a Shareplan group</t>
+          <t>The latest orders are displayed in the Latest Orders Table</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Shareplan group: 'In-plan', Billing account: '12345', Plan Name: 'Plan A', # of subscribers: 5, Allowance (MB): 1000, Used (MB): 500, Overage (MB): 200</t>
+          <t>At least one order has been placed by the user</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1117,7 +1073,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Detailed Table for Plans and Subscribers</t>
+          <t>Order and Shopping Management</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1127,12 +1083,12 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Selection of Individual Plans brings customer to separate table with listed details</t>
+          <t>View All Orders</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view a detailed breakdown of their individual plans after selecting an Individual Plan</t>
+          <t>Verify that the system provides the ability to view all orders</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1145,35 +1101,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>The customer has multiple Individual Plans and the user has the necessary permissions to view the Individual Plans Detail Table</t>
+          <t>User has placed at least one order</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the Usage Drilldown Table page
-2. Select an Individual Plan
-3. Click on the selected Individual Plan to view the detailed table
-4. Verify that the detailed table is displayed with the listed details: Number (MDN), Name, Billing account, Allowance (MB), Used (MB), and Overage (MB)
-5. Verify that the data is accurately representing the correct allowance, used, and overage
-6. Verify that the columns display numerical values in MB for allowance, used data, and overage within the same row
-7. Verify that the Back Button is implemented to bring the user back to the standard Usage Bar Chart Drilldown View</t>
+          <t>1. Navigate to the Shopping and Orders Widget
+2. Click the View All Orders link
+3. Verify all orders are displayed, including In Progress, Completed, and Cancelled orders</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>The user is able to view a detailed breakdown of their individual plans after selecting an Individual Plan</t>
+          <t>All orders are displayed, including In Progress, Completed, and Cancelled orders</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>Individual Plan: 'Plan B', Number (MDN): '1234567890', Name: 'John Doe', Billing account: '12345', Allowance (MB): 500, Used (MB): 200, Overage (MB): 100</t>
+          <t>At least one order has been placed by the user</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1190,7 +1142,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Detailed Table for Plans and Subscribers</t>
+          <t>Order and Shopping Management</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1200,12 +1152,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Data is sorted based on billing account's alphabetical order</t>
+          <t>Negative Test - No Orders</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Verify that the data is sorted based on the billing account's alphabetical order</t>
+          <t>Verify that the system handles the case where no orders have been placed</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1218,32 +1170,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>The customer has multiple billing accounts and the user has the necessary permissions to view the Shareplans Detail Table</t>
+          <t>User has not placed any orders</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Shareplans Detail Table page
-2. Verify that the data is sorted based on the billing account's alphabetical order
-3. Verify that the billing accounts are displayed in alphabetical order: '12345', '23456', '34567', etc.
-4. Verify that the data is accurately representing the correct allowance, used, and overage for each billing account</t>
+          <t>1. Navigate to the Shopping and Orders Widget
+2. Verify the Latest Orders Table is empty
+3. Click the View All Orders link
+4. Verify a message is displayed indicating no orders have been placed</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>The data is sorted based on the billing account's alphabetical order</t>
+          <t>A message is displayed indicating no orders have been placed</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Billing accounts: '12345', '23456', '34567', Allowance (MB): 1000, Used (MB): 500, Overage (MB): 200</t>
+          <t>No orders have been placed by the user</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1255,12 +1207,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>INUTS-003</t>
+          <t>INUTS-004</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Detailed Table for Plans and Subscribers</t>
+          <t>System Integration and Infrastructure</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1270,17 +1222,17 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Maximum of 10 Billing accounts displayed with pagination if more than 10 are in view</t>
+          <t>Verify System Integration with Kafka</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Verify that a maximum of 10 billing accounts are displayed with pagination if more than 10 are in view</t>
+          <t>Verify that the system integrates with Kafka to receive unbilled usages</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1288,32 +1240,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>The customer has more than 10 billing accounts and the user has the necessary permissions to view the Shareplans Detail Table</t>
+          <t>Kafka integration is enabled, IDD system is available</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the Shareplans Detail Table page
-2. Verify that a maximum of 10 billing accounts are displayed
-3. Verify that pagination is implemented to display more than 10 billing accounts
-4. Verify that the user can navigate to the next page to view the remaining billing accounts</t>
+          <t>1. Verify the system is connected to Kafka
+2. Send unbilled usages data from Kafka to the system
+3. Verify the system receives the unbilled usages data from Kafka
+4. Verify the system stores the unbilled usages data</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>A maximum of 10 billing accounts are displayed with pagination if more than 10 are in view</t>
+          <t>The system successfully integrates with Kafka and receives unbilled usages data</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>Billing accounts: '12345', '23456', '34567', '45678', '56789', '67890', '78901', '89012', '90123', '01234', '12345'</t>
+          <t>Unbilled usages data from Kafka</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
@@ -1325,12 +1277,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>INUTS-003</t>
+          <t>INUTS-004</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Detailed Table for Plans and Subscribers</t>
+          <t>System Integration and Infrastructure</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1340,12 +1292,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Billing account is selectable link and brings customer to preexisting my inventory section to display Billing account usage details page</t>
+          <t>Verify System Provides System Infrastructure</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Verify that the billing account is a selectable link and brings the customer to the preexisting my inventory section to display the Billing account usage details page</t>
+          <t>Verify that the system provides system infrastructure</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1365,25 +1317,24 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>The customer has multiple billing accounts and the user has the necessary permissions to view the Shareplans Detail Table</t>
+          <t>System infrastructure is enabled</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Shareplans Detail Table page
-2. Click on a billing account to view the Billing account usage details page
-3. Verify that the Billing account usage details page is displayed
-4. Verify that the page displays the usage details for the selected billing account</t>
+          <t>1. Verify the system provides key wireless management insights and actions in a single dashboard
+2. Verify the dashboard displays key metrics such as number of active subscribers, number of suspended subscribers, and total number of BANS
+3. Verify the dashboard displays usage at a glance, including plans in overage by thresholds</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>The billing account is a selectable link and brings the customer to the preexisting my inventory section to display the Billing account usage details page</t>
+          <t>The system provides system infrastructure and displays key metrics and usage at a glance</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Billing account: '12345', Usage details: 'Allowance (MB): 1000, Used (MB): 500, Overage (MB): 200'</t>
+          <t>Sample subscriber data</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1400,7 +1351,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>User Management and Access Control</t>
+          <t>System Integration and Infrastructure</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1410,17 +1361,17 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Create a new user</t>
+          <t>Verify Error Handling for Kafka Integration</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to create a new user</t>
+          <t>Verify that the system handles errors when integrating with Kafka</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1428,36 +1379,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>The user has the necessary permissions to manage users</t>
+          <t>Kafka integration is enabled, IDD system is available</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the User Management page
-2. Click the 'Create New User' button
-3. Enter 'john.doe@company.com' in the 'Email' field
-4. Enter 'John Doe' in the 'Full Name' field
-5. Select 'Active' from the 'Status' dropdown
-6. Click the 'Save' button
-7. Verify the new user is created successfully and visible in the user list
-8. Verify the confirmation message displays: 'User created successfully'</t>
+          <t>1. Simulate a Kafka connection error
+2. Verify the system displays an error message
+3. Verify the system retries the Kafka connection
+4. Verify the system logs the error</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>The new user is created successfully and visible in the user list</t>
+          <t>The system handles Kafka connection errors and retries the connection</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>john.doe@company.com, John Doe, Active</t>
+          <t>Error simulation data</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -1469,12 +1416,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>INUTS-004</t>
+          <t>INUTS-005</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>User Management and Access Control</t>
+          <t>Warranty Expiration Date Display</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1484,12 +1431,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Manage existing users</t>
+          <t>Display Warranty Expiration Date on Subscriber Page</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to manage existing users</t>
+          <t>Verify that the warranty expiration date is displayed on the Subscriber page</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1502,36 +1449,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>The user has the necessary permissions to manage users and at least one existing user</t>
+          <t>The user has a valid account and is logged in, with a device that has a warranty expiration date</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the User Management page
-2. Select an existing user from the user list
-3. Click the 'Edit' button
-4. Update the 'Full Name' field to 'Jane Doe'
-5. Select 'Inactive' from the 'Status' dropdown
-6. Click the 'Save' button
-7. Verify the user details are updated successfully
-8. Verify the confirmation message displays: 'User updated successfully'</t>
+          <t>1. Navigate to the Subscriber page
+2. Verify the Warranty expiration date is displayed in the Device Information page area
+3. Verify the Warranty expiration date corresponds to the date of activation
+4. Verify the Warranty expiration date is displayed for an OEM device</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>The user details are updated successfully</t>
+          <t>The warranty expiration date is displayed correctly on the Subscriber page</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>john.doe@company.com, Jane Doe, Inactive</t>
+          <t>A valid device with a warranty expiration date</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1543,12 +1486,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>INUTS-004</t>
+          <t>INUTS-005</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>User Management and Access Control</t>
+          <t>Warranty Expiration Date Display</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1558,12 +1501,12 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Create a new user with invalid credentials</t>
+          <t>Negative Test - No Warranty Expiration Date</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to create a new user with invalid credentials</t>
+          <t>Verify that no warranty expiration date is displayed when there is no warranty</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1583,28 +1526,23 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>The user has the necessary permissions to manage users</t>
+          <t>The user has a valid account and is logged in, with a device that does not have a warranty expiration date</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the User Management page
-2. Click the 'Create New User' button
-3. Enter 'invalid_email' in the 'Email' field
-4. Enter 'John Doe' in the 'Full Name' field
-5. Select 'Active' from the 'Status' dropdown
-6. Click the 'Save' button
-7. Verify an error message displays: 'Invalid email address'</t>
+          <t>1. Navigate to the Subscriber page
+2. Verify that no Warranty expiration date is displayed in the Device Information page area</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>An error message displays: 'Invalid email address'</t>
+          <t>No warranty expiration date is displayed</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>invalid_email, John Doe, Active</t>
+          <t>A device without a warranty expiration date</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1621,7 +1559,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Export Feature Implementation</t>
+          <t>Warranty Expiration Date Display</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1631,12 +1569,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Export Data in CSV Format</t>
+          <t>Boundary Test - Warranty Expiration Date in the Past</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to export data in CSV format</t>
+          <t>Verify that the warranty expiration date is displayed correctly when it is in the past</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1649,39 +1587,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>User has valid credentials and dashboard is accessible</t>
+          <t>The user has a valid account and is logged in, with a device that has a warranty expiration date in the past</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter valid username in the 'Email' field
-3. Enter valid password in the 'Password' field
-4. Click the 'Sign In' button
-5. Navigate to the dashboard
-6. Click on the 'Export Feature' option
-7. Select 'CSV' as the export file format
-8. Verify the CSV file is downloaded successfully
-9. Open the downloaded CSV file and verify it contains the expected data
-10. Verify the CSV file includes the Bar Graph data, Voice, SMS, and LD Usages
-11. Verify the CSV file includes the grouped data upon Graph selection</t>
+          <t>1. Navigate to the Subscriber page
+2. Verify the Warranty expiration date is displayed in the Device Information page area
+3. Verify the Warranty expiration date is in the past</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>The user is able to export data in CSV format and the file contains the expected data</t>
+          <t>The warranty expiration date is displayed correctly</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Valid username: john.doe@company.com, Valid password: password123</t>
+          <t>A device with a warranty expiration date in the past</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1693,12 +1623,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>INUTS-005</t>
+          <t>INUTS-006</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Export Feature Implementation</t>
+          <t>Selectable Data Groupings</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1708,12 +1638,12 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Export Data in PDF Format</t>
+          <t>Selectable Data Groupings Default View</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to export data in PDF format</t>
+          <t>Verify that the default grouping is 'Data' and the dashboard view switches between Data, Voice, Long Distance, and SMS</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1726,39 +1656,33 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>User has valid credentials and dashboard is accessible</t>
+          <t>User is logged in and has access to the dashboard</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter valid username in the 'Email' field
-3. Enter valid password in the 'Password' field
-4. Click the 'Sign In' button
-5. Navigate to the dashboard
-6. Click on the 'Export Feature' option
-7. Select 'PDF' as the export file format
-8. Verify the PDF file is downloaded successfully
-9. Open the downloaded PDF file and verify it contains the expected data
-10. Verify the PDF file includes the Bar Graph data, Voice, SMS, and LD Usages
-11. Verify the PDF file includes the tabled data</t>
+          <t>1. Verify the 'Data' grouping is selected by default
+2. Click on the 'Voice' grouping and verify the dashboard view changes to display Voice data
+3. Click on the 'Long Distance' grouping and verify the dashboard view changes to display Long Distance data
+4. Click on the 'SMS' grouping and verify the dashboard view changes to display SMS data
+5. Verify the grouping state persists across reloads</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>The user is able to export data in PDF format and the file contains the expected data</t>
+          <t>The dashboard view switches between Data, Voice, Long Distance, and SMS groupings, and the state persists across reloads</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>Valid username: john.doe@company.com, Valid password: password123</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1770,12 +1694,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>INUTS-005</t>
+          <t>INUTS-006</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Export Feature Implementation</t>
+          <t>Selectable Data Groupings</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1785,12 +1709,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Export Data in Invalid Format</t>
+          <t>Selectable Data Groupings Navigation</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is not able to export data in an invalid format</t>
+          <t>Verify that the grouping state persists when navigating from group to group</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1803,37 +1727,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>User has valid credentials and dashboard is accessible</t>
+          <t>User is logged in and has access to the dashboard</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter valid username in the 'Email' field
-3. Enter valid password in the 'Password' field
-4. Click the 'Sign In' button
-5. Navigate to the dashboard
-6. Click on the 'Export Feature' option
-7. Select an invalid file format
-8. Verify an error message is displayed
-9. Verify the error message indicates that the selected format is not supported</t>
+          <t>1. Select the 'Voice' grouping and verify the dashboard view changes to display Voice data
+2. Navigate to the 'My Inventory' menu item and then return to the dashboard
+3. Verify the 'Voice' grouping is still selected
+4. Repeat steps 1-3 for 'Long Distance' and 'SMS' groupings</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>The user is not able to export data in an invalid format and an error message is displayed</t>
+          <t>The grouping state persists when navigating from group to group</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Valid username: john.doe@company.com, Valid password: password123, Invalid file format: TXT</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1850,7 +1769,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Grey Market Device Requirements</t>
+          <t>Selectable Data Groupings</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1860,12 +1779,12 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Warranty Information Display for BYOD Devices</t>
+          <t>Selectable Data Groupings Error Handling</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view accurate warranty information for their BYOD device</t>
+          <t>Verify that an error message is displayed when an invalid grouping is selected</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1878,38 +1797,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>The user has a BYOD device registered in their profile and has the necessary permissions to view warranty information</t>
+          <t>User is logged in and has access to the dashboard</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Subscriber Information page
-2. Step 2: Locate the Warranty Information section within the Subscriber Information page
-3. Step 3: Verify that the Warranty Date is displayed and is accurate towards the customer's activation date associated with the device currently on their profile
-4. Step 4: Verify that the Warranty Date is displayed within the specific line as per the visuals attached as reference
-5. Step 5: Verify that the warranty information is up-to-date and reflects the current warranty status of the device
-6. Step 6: Test with a device that has no active warranty and verify that the correct message is displayed (e.g. 'No active warranty')
-7. Step 7: Test with a device that has an expired warranty and verify that the correct message is displayed (e.g. 'Warranty expired')
-8. Step 8: Test with a device that has a valid warranty and verify that the correct warranty information is displayed
-9. Step 9: Verify that the warranty information is displayed in the correct format and is easy to read
-10. Step 10: Log out of the system and verify that the warranty information is no longer accessible</t>
+          <t>1. Attempt to select an invalid grouping (e.g. a non-existent grouping)
+2. Verify an error message is displayed
+3. Verify the dashboard view does not change</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>The user is able to view accurate and up-to-date warranty information for their BYOD device</t>
+          <t>An error message is displayed and the dashboard view does not change</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>Test data: BYOD device with a valid warranty, BYOD device with no active warranty, BYOD device with an expired warranty</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -1921,12 +1833,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>INUTS-006</t>
+          <t>INUTS-007</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Grey Market Device Requirements</t>
+          <t>Monthly Bar Chart Display</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1936,12 +1848,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Warranty Information Display for Dealer Devices</t>
+          <t>Verify Monthly Bar Chart Display</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view accurate warranty information for their dealer device</t>
+          <t>Verify that the system displays a monthly Bar Chart reflecting data usage for the last 14 months</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1961,31 +1873,26 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>The user has a dealer device registered in their profile and has the necessary permissions to view warranty information</t>
+          <t>User has access to the Play to Win Solutions Page</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Subscriber Information page
-2. Step 2: Locate the Warranty Information section within the Subscriber Information page
-3. Step 3: Verify that the Warranty Date is displayed and is accurate towards the customer's activation date associated with the device currently on their profile
-4. Step 4: Verify that the Warranty Date is displayed within the specific line as per the visuals attached as reference
-5. Step 5: Verify that the warranty information is up-to-date and reflects the current warranty status of the device
-6. Step 6: Test with a device that has no active warranty and verify that the correct message is displayed (e.g. 'No active warranty')
-7. Step 7: Test with a device that has an expired warranty and verify that the correct message is displayed (e.g. 'Warranty expired')
-8. Step 8: Test with a device that has a valid warranty and verify that the correct warranty information is displayed
-9. Step 9: Verify that the warranty information is displayed in the correct format and is easy to read
-10. Step 10: Log out of the system and verify that the warranty information is no longer accessible</t>
+          <t>1. Navigate to the Play to Win Solutions Page
+2. Verify the monthly Bar Chart is displayed
+3. Verify the Bar Chart reflects data usage for the last 14 months
+4. Verify the Bar Chart displays Data, Voice, SMS and LD usages
+5. Verify the Bar Chart displays breakdown of Roaming, Overage and In-plan usages</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>The user is able to view accurate and up-to-date warranty information for their dealer device</t>
+          <t>The system displays a monthly Bar Chart reflecting data usage for the last 14 months</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Test data: Dealer device with a valid warranty, Dealer device with no active warranty, Dealer device with an expired warranty</t>
+          <t>Last 14 months of data usage</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1997,12 +1904,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>INUTS-006</t>
+          <t>INUTS-007</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Grey Market Device Requirements</t>
+          <t>Monthly Bar Chart Display</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2012,12 +1919,12 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Negative Testing - Invalid Device</t>
+          <t>Verify Bar Chart Drill-Down Functionality</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Verify that the system handles invalid devices correctly</t>
+          <t>Verify that the user can drill down on details of both billed and unbilled usages of the Customer's NAG</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2037,28 +1944,25 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>The user has an invalid device registered in their profile</t>
+          <t>User has access to the Play to Win Solutions Page and has a NAG with billed and unbilled usages</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Subscriber Information page
-2. Step 2: Locate the Warranty Information section within the Subscriber Information page
-3. Step 3: Verify that an error message is displayed indicating that the device is invalid
-4. Step 4: Verify that the warranty information is not displayed for the invalid device
-5. Step 5: Test with different types of invalid devices (e.g. device not registered, device not activated)
-6. Step 6: Verify that the system handles each type of invalid device correctly
-7. Step 7: Log out of the system and verify that the warranty information is no longer accessible</t>
+          <t>1. Navigate to the Play to Win Solutions Page
+2. Click on the Bar Chart to drill down on details
+3. Verify the details of both billed and unbilled usages of the Customer's NAG are displayed
+4. Verify the user can view the breakdown of Roaming, Overage and In-plan usages</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>The system handles invalid devices correctly and does not display warranty information for them</t>
+          <t>The user can drill down on details of both billed and unbilled usages of the Customer's NAG</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>Test data: Invalid device, Device not registered, Device not activated</t>
+          <t>NAG with billed and unbilled usages</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -2075,7 +1979,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Data Units and Colour Coding</t>
+          <t>Monthly Bar Chart Display</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2085,12 +1989,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>View Data Units and Colour Coding for Usage Types</t>
+          <t>Verify Bar Chart Error Handling</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view data units and colour coding for usage types such as minutes, messages, and MB/GB</t>
+          <t>Verify that the system handles errors when displaying the monthly Bar Chart</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2103,38 +2007,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>The user has mydashboard-view or mydashboard-manage permissions and has usage access</t>
+          <t>User has access to the Play to Win Solutions Page</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the dashboard
-2. Step 2: Verify the dashboard displays data units for usage types such as minutes, messages, and MB/GB
-3. Step 3: Verify the dashboard displays colour coding for usage types
-4. Step 4: Verify the colour coding scheme is consistent and intuitive
-5. Step 5: Verify the user can view unbilled usage for the current month
-6. Step 6: Verify the user can view billed usage for previous months
-7. Step 7: Verify the user can drill down to specific customers from the dashboard
-8. Step 8: Verify the dashboard does not display daily or weekly separate capture of unbilled usage
-9. Step 9: Verify the dashboard only displays monthly view of unbilled usage
-10. Step 10: Verify the user can view usage data in a clear and understandable format</t>
+          <t>1. Navigate to the Play to Win Solutions Page
+2. Simulate an error when displaying the Bar Chart
+3. Verify an error message is displayed to the user
+4. Verify the error message is descriptive and helpful</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>The dashboard displays data units and colour coding for usage types, and the user can view usage data in a clear and understandable format</t>
+          <t>The system handles errors when displaying the monthly Bar Chart</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Sample usage data for minutes, messages, and MB/GB</t>
+          <t>Error simulation</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2146,12 +2044,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>INUTS-007</t>
+          <t>INUTS-008</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Data Units and Colour Coding</t>
+          <t>Drilldown View</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2161,12 +2059,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Invalid or Missing Usage Data</t>
+          <t>Drilldown View for Bar Graph Selection</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to view data units and colour coding for usage types when usage data is invalid or missing</t>
+          <t>Verify that the user is able to view a drilldown reflecting data when a Bar Graph is selected</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2179,36 +2077,33 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>The user has mydashboard-view or mydashboard-manage permissions but does not have usage access</t>
+          <t>The user has access to the Usage Bar Chart and can view the graph bars</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the dashboard
-2. Step 2: Verify the dashboard does not display data units for usage types
-3. Step 3: Verify the dashboard does not display colour coding for usage types
-4. Step 4: Verify the user is unable to view unbilled usage for the current month
-5. Step 5: Verify the user is unable to view billed usage for previous months
-6. Step 6: Verify the user is unable to drill down to specific customers from the dashboard
-7. Step 7: Verify the dashboard displays an error message or notification when usage data is invalid or missing
-8. Step 8: Verify the user can navigate away from the dashboard and return to the login page</t>
+          <t>1. Click on a graph bar to show details
+2. Verify the drilldown view loads data corresponding to the specific month selected
+3. Verify the heading reflects the month selected, e.g., 'March 2025 data usage'
+4. Verify the data is accurate towards the specific month selected
+5. Verify the billed usage provides a user usage summary table</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>The dashboard does not display data units and colour coding for usage types, and the user is unable to view usage data</t>
+          <t>The drilldown view displays the correct data for the selected month and provides a usage summary table</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>Invalid or missing usage data for minutes, messages, and MB/GB</t>
+          <t>Select a specific month, e.g., March 2025, and verify the data</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -2225,7 +2120,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Back Button Navigation</t>
+          <t>Drilldown View</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2235,12 +2130,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Back Button Navigation to Previous View</t>
+          <t>Shared Plans Usage Breakdown in Drilldown View</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to navigate back to the previous view using the Back Button</t>
+          <t>Verify that the user can view a breakdown of shared plans within each category in the drilldown view</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2253,36 +2148,33 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>The user is logged in and has navigated to a view with a Back Button</t>
+          <t>The user has access to the Usage Bar Chart and can view the graph bars</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Usage Summary Tabs
-2. Step 2: Click on the Data Usage Bar Chart to drill down
-3. Step 3: Verify the Interaction Prompt is visible
-4. Step 4: Click on the Back Button to navigate back to the previous view
-5. Step 5: Verify the user is brought back to the previous view with the Interaction Prompt visible
-6. Step 6: Repeat steps 2-5 with different views, such as the Shared Plans Usage Breakdown and Individual Plans Usage Breakdown
-7. Step 7: Verify the Back Button works correctly for each view
-8. Step 8: Test the Back Button with different NAG (Group) Filter selections</t>
+          <t>1. Click on a graph bar to show details
+2. Verify the Shared Plans table is displayed with a breakdown of roaming, overage, and in-plan usage
+3. Verify the share group for plans is broken down accurately, e.g., 'Small/Medium/Large business share plan'
+4. Verify the data is accurate towards usage for each group
+5. Verify the links are clickable for each group's corresponding Data Usage category</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>The user is able to navigate back to the previous view with the Interaction Prompt visible</t>
+          <t>The Shared Plans table displays the correct breakdown of shared plans within each category</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Usage Summary Tabs, Data Usage Bar Chart, Interaction Prompt, Shared Plans Usage Breakdown, Individual Plans Usage Breakdown, NAG (Group) Filter</t>
+          <t>Select a specific shared plan, e.g., 'Small business share plan', and verify the data</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2299,7 +2191,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Back Button Navigation</t>
+          <t>Drilldown View</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2309,12 +2201,12 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Back Button Navigation with Empty Input</t>
+          <t>Individual Plans Usage Breakdown in Drilldown View</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to navigate back to the previous view using the Back Button with empty input</t>
+          <t>Verify that the user can view a breakdown of individual plans in the drilldown view</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -2327,36 +2219,33 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>The user is logged in and has navigated to a view with a Back Button</t>
+          <t>The user has access to the Usage Bar Chart and can view the graph bars</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Usage Summary Tabs
-2. Step 2: Clear any input fields, such as the NAG (Group) Filter
-3. Step 3: Click on the Data Usage Bar Chart to drill down
-4. Step 4: Verify the Interaction Prompt is visible
-5. Step 5: Click on the Back Button to navigate back to the previous view
-6. Step 6: Verify the user is brought back to the previous view with the Interaction Prompt visible
-7. Step 7: Repeat steps 2-6 with different views, such as the Shared Plans Usage Breakdown and Individual Plans Usage Breakdown
-8. Step 8: Verify the Back Button works correctly for each view with empty input</t>
+          <t>1. Click on a graph bar to show details
+2. Verify the Individual Plans table is displayed with a breakdown of roaming, overage, and in-plan usage
+3. Verify the individual plans for the number of subscribers are broken down accurately
+4. Verify the data is accurate towards usage for each group
+5. Verify the data reflects MB, Voice and Long Distance reflects Minutes, and Text Messaging reflects Numbers</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>The user is able to navigate back to the previous view with the Interaction Prompt visible, even with empty input</t>
+          <t>The Individual Plans table displays the correct breakdown of individual plans</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>Usage Summary Tabs, Data Usage Bar Chart, Interaction Prompt, Shared Plans Usage Breakdown, Individual Plans Usage Breakdown, NAG (Group) Filter</t>
+          <t>Select a specific individual plan, e.g., 'Plan A', and verify the data</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
@@ -2368,12 +2257,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>INUTS-008</t>
+          <t>INUTS-009</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Back Button Navigation</t>
+          <t>Shared Plans Usage Breakdown</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2383,12 +2272,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Back Button Navigation with Invalid Input</t>
+          <t>Verify Shared Plans Usage Breakdown Table</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to navigate back to the previous view using the Back Button with invalid input</t>
+          <t>Verify that the user is able to view a table summarizing roaming, overage, and in-plan usage for shared plans</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2401,36 +2290,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>The user is logged in and has navigated to a view with a Back Button</t>
+          <t>User has a shared plan and is logged in to the dashboard</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Usage Summary Tabs
-2. Step 2: Enter invalid input, such as a non-existent NAG (Group) Filter value
-3. Step 3: Click on the Data Usage Bar Chart to drill down
-4. Step 4: Verify the Interaction Prompt is visible
-5. Step 5: Click on the Back Button to navigate back to the previous view
-6. Step 6: Verify the user is brought back to the previous view with the Interaction Prompt visible
-7. Step 7: Repeat steps 2-6 with different views, such as the Shared Plans Usage Breakdown and Individual Plans Usage Breakdown
-8. Step 8: Verify the Back Button works correctly for each view with invalid input</t>
+          <t>1. Navigate to the Shared Plans Usage Breakdown section
+2. Verify the table displays columns for roaming, overage, and in-plan usage
+3. Verify the table shows the correct usage data for the shared plan
+4. Verify the table is sortable and filterable by usage type</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>The user is able to navigate back to the previous view with the Interaction Prompt visible, even with invalid input</t>
+          <t>The table displays the correct usage data for the shared plan, and is sortable and filterable by usage type</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>Usage Summary Tabs, Data Usage Bar Chart, Interaction Prompt, Shared Plans Usage Breakdown, Individual Plans Usage Breakdown, NAG (Group) Filter</t>
+          <t>Shared plan with roaming, overage, and in-plan usage data</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2447,7 +2332,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Quick Links Area</t>
+          <t>Shared Plans Usage Breakdown</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -2457,12 +2342,12 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>View Quick Links Area</t>
+          <t>Verify Shared Plans Usage Breakdown Table with No Data</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view the quick links area</t>
+          <t>Verify that the user is able to view a table summarizing roaming, overage, and in-plan usage for shared plans with no data</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2475,38 +2360,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>The user must be logged in as a BBM wireless subscriber</t>
+          <t>User has a shared plan with no usage data and is logged in to the dashboard</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the dashboard
-2. Step 2: Verify the quick links area is displayed
-3. Step 3: Verify the quick links area contains links to other Bell tools
-4. Step 4: Click on a link in the quick links area
-5. Step 5: Verify the user is redirected to the corresponding Bell tool
-6. Step 6: Verify the user can access the Bell tool without any errors
-7. Step 7: Click on the back button to return to the dashboard
-8. Step 8: Verify the user is returned to the dashboard
-9. Step 9: Verify the quick links area is still displayed
-10. Step 10: Verify the links in the quick links area are still functional</t>
+          <t>1. Navigate to the Shared Plans Usage Breakdown section
+2. Verify the table displays a message indicating no data is available
+3. Verify the table does not display any usage data</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>The user is able to view the quick links area and access other Bell tools</t>
+          <t>The table displays a message indicating no data is available, and does not display any usage data</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>Test data: BBM wireless subscriber credentials</t>
+          <t>Shared plan with no usage data</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2523,7 +2401,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Quick Links Area</t>
+          <t>Shared Plans Usage Breakdown</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2533,12 +2411,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Access Other Bell Tools</t>
+          <t>Verify Shared Plans Usage Breakdown Table with Invalid Data</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to access other Bell tools from the quick links area</t>
+          <t>Verify that the user is able to view a table summarizing roaming, overage, and in-plan usage for shared plans with invalid data</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2551,38 +2429,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>The user must be logged in as a BBM wireless subscriber and have access to other Bell tools</t>
+          <t>User has a shared plan with invalid usage data and is logged in to the dashboard</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the dashboard
-2. Step 2: Verify the quick links area is displayed
-3. Step 3: Click on a link in the quick links area
-4. Step 4: Verify the user is redirected to the corresponding Bell tool
-5. Step 5: Verify the user can access the Bell tool without any errors
-6. Step 6: Perform an action in the Bell tool (e.g. view account information)
-7. Step 7: Verify the action is successful
-8. Step 8: Click on the back button to return to the dashboard
-9. Step 9: Verify the user is returned to the dashboard
-10. Step 10: Verify the quick links area is still displayed</t>
+          <t>1. Navigate to the Shared Plans Usage Breakdown section
+2. Verify the table displays an error message indicating invalid data
+3. Verify the table does not display any usage data</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>The user is able to access other Bell tools from the quick links area</t>
+          <t>The table displays an error message indicating invalid data, and does not display any usage data</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Test data: BBM wireless subscriber credentials and access to other Bell tools</t>
+          <t>Shared plan with invalid usage data</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2594,12 +2465,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>INUTS-009</t>
+          <t>INUTS-010</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Quick Links Area</t>
+          <t>In-plan Usage Threshold Donut Wheel</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2609,12 +2480,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Invalid Access to Other Bell Tools</t>
+          <t>Donut Wheel Rendering for Under 75% Usage</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is not able to access other Bell tools without proper authorization</t>
+          <t>Verify that the Donut Wheel renders accordingly for under 75% usage</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2627,38 +2498,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>The user must be logged in as a BBM wireless subscriber without access to other Bell tools</t>
+          <t>User has a valid account with current month's usage data</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the dashboard
-2. Step 2: Verify the quick links area is displayed
-3. Step 3: Click on a link in the quick links area
-4. Step 4: Verify the user is not redirected to the corresponding Bell tool
-5. Step 5: Verify an error message is displayed indicating that the user does not have access to the Bell tool
-6. Step 6: Verify the user is returned to the dashboard
-7. Step 7: Verify the quick links area is still displayed
-8. Step 8: Verify the links in the quick links area are still functional
-9. Step 9: Verify the user cannot access the Bell tool without proper authorization
-10. Step 10: Verify the error message is still displayed</t>
+          <t>1. Verify the Donut Wheel is displayed on the page
+2. Verify the Donut Wheel shows usage under 75%
+3. Verify the Donut Wheel color corresponds to the under 75% threshold</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>The user is not able to access other Bell tools without proper authorization</t>
+          <t>The Donut Wheel is displayed and shows usage under 75% with the correct color</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Test data: BBM wireless subscriber credentials without access to other Bell tools</t>
+          <t>Current month's usage data with 50% usage</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
@@ -2675,7 +2539,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Show Button</t>
+          <t>In-plan Usage Threshold Donut Wheel</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2685,12 +2549,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>View Additional Information Using Show Button</t>
+          <t>Donut Wheel Rendering for 75-95% Usage</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view additional information by clicking the show button</t>
+          <t>Verify that the Donut Wheel renders accordingly for 75-95% usage</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2710,30 +2574,24 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>User has necessary permissions and additional information is available</t>
+          <t>User has a valid account with current month's usage data</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the page with the show button
-2. Verify the show button is displayed
-3. Click the show button
-4. Verify additional information is displayed
-5. Verify the user can view the additional information without any errors
-6. Click the show button again to hide the additional information
-7. Verify the additional information is hidden
-8. Enter invalid input to test error handling
-9. Verify an error message is displayed</t>
+          <t>1. Verify the Donut Wheel is displayed on the page
+2. Verify the Donut Wheel shows usage between 75% and 95%
+3. Verify the Donut Wheel color corresponds to the 75-95% threshold</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>The user is able to view additional information by clicking the show button and the information is displayed correctly</t>
+          <t>The Donut Wheel is displayed and shows usage between 75% and 95% with the correct color</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Sample additional information</t>
+          <t>Current month's usage data with 85% usage</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2750,7 +2608,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Show Button</t>
+          <t>In-plan Usage Threshold Donut Wheel</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -2760,12 +2618,12 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Show Button Error Handling</t>
+          <t>Donut Wheel Rendering for Over 95% Usage</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Verify that the show button handles errors correctly</t>
+          <t>Verify that the Donut Wheel renders accordingly for over 95% usage</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2778,36 +2636,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>User has necessary permissions and additional information is available</t>
+          <t>User has a valid account with current month's usage data</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the page with the show button
-2. Verify the show button is displayed
-3. Click the show button without necessary permissions
-4. Verify an error message is displayed
-5. Click the show button with invalid input
-6. Verify an error message is displayed
-7. Click the show button with missing required fields
-8. Verify an error message is displayed</t>
+          <t>1. Verify the Donut Wheel is displayed on the page
+2. Verify the Donut Wheel shows usage over 95%
+3. Verify the Donut Wheel color corresponds to the over 95% threshold</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>The show button handles errors correctly and displays an error message</t>
+          <t>The Donut Wheel is displayed and shows usage over 95% with the correct color</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>Sample invalid input</t>
+          <t>Current month's usage data with 100% usage</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -2824,7 +2677,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>User Roles and Permissions</t>
+          <t>Breakdown Table Back Button</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2834,12 +2687,12 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Valid User Credentials with Correct Role and Permissions</t>
+          <t>Back Button Navigation to 14-Month Bar Chart View</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to access the dashboard based on their role and permissions</t>
+          <t>Verify that the user is able to navigate back to the 14-month bar chart view using the back button within the Breakdown Table</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2852,37 +2705,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>The user roles and permissions are correctly configured in the system</t>
+          <t>The user is currently viewing the Breakdown Table</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter 'john.doe@company.com' in the 'Email' field
-3. Enter 'password123' in the 'Password' field
-4. Click the 'Sign In' button
-5. Verify the dashboard displays the correct level of usage information based on the user's role and permissions
-6. Verify the user is able to view the 'Latest Orders Table'
-7. Verify the user is able to view the 'Shopping and Orders Widget'
-8. Click the 'Back Button to Drill down table' and verify the user is able to navigate back to the previous page
-9. Logout from the dashboard</t>
+          <t>1. Click the Back Button within the Breakdown Table
+2. Verify the 14-month bar chart view is displayed
+3. Verify the Interaction Prompt is visible</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>The dashboard displays the correct level of usage information based on the user's role and permissions</t>
+          <t>The user is navigated back to the 14-month bar chart view with the Interaction Prompt visible</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>john.doe@company.com, password123</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2899,7 +2746,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>User Roles and Permissions</t>
+          <t>Breakdown Table Back Button</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -2909,12 +2756,12 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Invalid User Credentials or Incorrect Role and Permissions</t>
+          <t>Back Button Navigation with No Interaction Prompt</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is not able to access the dashboard with invalid credentials or incorrect role and permissions</t>
+          <t>Verify that the user is able to navigate back to the 14-month bar chart view using the back button within the Breakdown Table when there is no Interaction Prompt</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2927,35 +2774,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>The user roles and permissions are correctly configured in the system</t>
+          <t>The user is currently viewing the Breakdown Table and there is no Interaction Prompt</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter 'invalid.user@company.com' in the 'Email' field
-3. Enter 'wrongpassword' in the 'Password' field
-4. Click the 'Sign In' button
-5. Verify an error message displays: 'Invalid username or password'
-6. Verify the user is not able to access the dashboard
-7. Logout from the login page</t>
+          <t>1. Click the Back Button within the Breakdown Table
+2. Verify the 14-month bar chart view is displayed
+3. Verify there is no Interaction Prompt visible</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>An error message displays: 'Invalid username or password'</t>
+          <t>The user is navigated back to the 14-month bar chart view with no Interaction Prompt visible</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>invalid.user@company.com, wrongpassword</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -2972,7 +2815,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Prevent Regression of Defect SADRSTRANG-13583</t>
+          <t>Individual Plans Detail Table Display</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2982,17 +2825,17 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Prevent Regression of Defect SADRSTRANG-13583</t>
+          <t>Verify Individual Plans Detail Table Display</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to use the system reliably without exhibiting the defect SADRSTRANG-13583</t>
+          <t>Verify that the user is able to view detailed information about individual plans</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3000,36 +2843,33 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>The system has been updated to prevent regression of defect SADRSTRANG-13583, and the user has a valid BBM wireless subscription</t>
+          <t>User has access to the Individual Plans Detail Table</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the BBSSC dashboard
-2. Verify the display of Data, Voice, SMS and LD usages in a clear display
-3. Click on the NAG Metric Tiles to view usage summary
-4. Verify the breakdown of Roaming, Overage and In-plan usages for each insight
-5. Drill down on details of both billed and unbilled usages of the Customer's NAG
-6. Verify the display of Shopping and orders insights - In progress, completed and cancelled
-7. Click on the quick links area to connect to other Bell tools
-8. Verify that the system does not exhibit the defect SADRSTRANG-13583</t>
+          <t>1. Select the Data Usage type from the dropdown filter
+2. Verify the # of individual plan subscribers is displayed
+3. Click on the # of individual plan subscribers
+4. Verify a separate table with listed details is displayed
+5. Verify the table includes columns for individual plan details</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>The user is able to use the system reliably without exhibiting the defect SADRSTRANG-13583</t>
+          <t>The user is able to view detailed information about individual plans in a separate table</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Valid BBM wireless subscription credentials</t>
+          <t>Sample data for individual plans</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3046,7 +2886,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Prevent Regression of Defect SADRSTRANG-13583</t>
+          <t>Individual Plans Detail Table Display</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -3056,17 +2896,17 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Negative Test - Invalid Input</t>
+          <t>Verify Error Handling for Invalid Input</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to use the system with invalid input</t>
+          <t>Verify that the system handles invalid input for individual plans detail table display</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -3074,33 +2914,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>The system has been updated to prevent regression of defect SADRSTRANG-13583, and the user has a valid BBM wireless subscription</t>
+          <t>User has access to the Individual Plans Detail Table</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the BBSSC dashboard
-2. Enter invalid credentials
-3. Click on the NAG Metric Tiles to view usage summary
-4. Verify that the system displays an error message
-5. Verify that the system does not exhibit the defect SADRSTRANG-13583</t>
+          <t>1. Enter an invalid Data Usage type
+2. Verify an error message is displayed
+3. Verify the error message indicates the invalid input
+4. Verify the system does not crash or become unresponsive</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>The user is unable to use the system with invalid input, and the system does not exhibit the defect SADRSTRANG-13583</t>
+          <t>The system handles invalid input and displays an error message</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>Invalid BBM wireless subscription credentials</t>
+          <t>Invalid data for individual plans</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
@@ -3112,12 +2951,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>INUTS-013</t>
+          <t>INUTS-012</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Billed Month Drilldown</t>
+          <t>Individual Plans Detail Table Display</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3127,17 +2966,17 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Billed Month Drilldown Test</t>
+          <t>Verify Boundary Case for Large Number of Individual Plans</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to drill down into their billed month data</t>
+          <t>Verify that the system handles a large number of individual plans</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3145,40 +2984,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>User has necessary permissions to view billed month data</t>
+          <t>User has access to the Individual Plans Detail Table with a large number of plans</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the 14-month bar chart view
-2. Select the current unbilled month
-3. Click on the Usage Bar Chart Drilldown
-4. Verify the In-Plan Usage Thresholds table is displayed with title and thresholds (75%, 75%-95%, 95%+)
-5. Verify the donut wheel showcases the number of individual plans within each threshold
-6. Click on a specific threshold (e.g. 75%)
-7. Verify the corresponding number of individual plans within that threshold is displayed
-8. Verify the color delineation between Usage types (In-plan, Overage, and Roaming) is according to agreed standards
-9. Click on the Shareplans Detail Table link for a specific usage type
-10. Verify the detailed table is displayed with columns for Billing Account, Plan Name, # of subscribers, Allowance (MB), Used (MB), and Overage (MB)
-11. Verify the data is sorted by billing account's alphabetical order
-12. Verify the data accurately represents the correct allowance, used, and overage values</t>
+          <t>1. Select a large number of individual plans
+2. Verify the system displays all plans in the table
+3. Verify the system does not become unresponsive or crash
+4. Verify the table is scrollable and sortable</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>The user is able to drill down into their billed month data and view the correct usage thresholds and shareplan details</t>
+          <t>The system handles a large number of individual plans and displays them in the table</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Sample test data: select the current unbilled month, click on the 75% threshold, verify the corresponding number of individual plans is displayed</t>
+          <t>Large number of individual plans</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3195,7 +3026,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Billed Month Drilldown</t>
+          <t>Shop now Button Functionality</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -3205,17 +3036,17 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Billed Month Drilldown Error Handling Test</t>
+          <t>Shop now Button Click</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to drill down into their billed month data without necessary permissions</t>
+          <t>Verify that the user is able to click the Shop now button and navigate to the correct URL</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -3223,34 +3054,30 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>User does not have necessary permissions to view billed month data</t>
+          <t>User is on the Shopping and orders box page</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the 14-month bar chart view
-2. Select the current unbilled month
-3. Attempt to click on the Usage Bar Chart Drilldown
-4. Verify an error message is displayed indicating that the user does not have necessary permissions
-5. Verify the In-Plan Usage Thresholds table is not displayed
-6. Verify the donut wheel is not displayed</t>
+          <t>1. Click the Shop now button on the top right of the Shopping and orders box
+2. Verify the URL in the new browser tab is https://shop.enterprisecentre.bell.ca/devices</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>The user is unable to drill down into their billed month data and an error message is displayed</t>
+          <t>The user is navigated to the correct URL in a new browser tab</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>Sample test data: attempt to drill down without necessary permissions</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
@@ -3262,12 +3089,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>INUTS-014</t>
+          <t>INUTS-013</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Unified Dashboard for Wireless Management Insights</t>
+          <t>Shop now Button Functionality</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3277,12 +3104,12 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Viewing Data Usage in Unified Dashboard</t>
+          <t>Shop now Button Placement</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view data usage through graphical design in the Unified Dashboard for Wireless Management Insights</t>
+          <t>Verify that the Shop now button is placed correctly on the Shopping and orders box page</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3295,37 +3122,30 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>The user has a valid login credentials and has access to the Unified Dashboard for Wireless Management Insights</t>
+          <t>User is on the Shopping and orders box page</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter valid username in the 'Email' field, e.g., 'john.doe@company.com'
-3. Enter valid password in the 'Password' field, e.g., 'password123'
-4. Click the 'Sign In' button
-5. Click on the 'Unified Dashboard for Wireless Management Insights' link
-6. Verify the 'Data' usage is displayed through graphical design
-7. Verify the breakdown of 'Roaming', 'Overage', and 'In-plan' usages for 'Data' insight is displayed
-8. Verify the user can drill down on details of both billed and unbilled usages of the Customer's NAG
-9. Verify the 'Data' usage graph updates when the user selects a different time period from the dropdown</t>
+          <t>1. Verify the Shop now button is displayed on the top right of the Shopping and orders box
+2. Verify the button is clickable</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>The user is able to view data usage through graphical design in the Unified Dashboard for Wireless Management Insights, with breakdown of roaming, overage, and in-plan usages</t>
+          <t>The Shop now button is displayed and clickable on the top right of the Shopping and orders box</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>john.doe@company.com, password123</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -3342,7 +3162,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Unified Dashboard for Wireless Management Insights</t>
+          <t>Export Feature</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -3352,12 +3172,12 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Viewing Voice Usage in Unified Dashboard</t>
+          <t>Export Dashboard Details in CSV Format</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view voice usage through graphical design in the Unified Dashboard for Wireless Management Insights</t>
+          <t>Verify that the user is able to export dashboard details in CSV format</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3370,37 +3190,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>The user has a valid login credentials and has access to the Unified Dashboard for Wireless Management Insights</t>
+          <t>User has access to the dashboard and has permission to export data</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter valid username in the 'Email' field, e.g., 'john.doe@company.com'
-3. Enter valid password in the 'Password' field, e.g., 'password123'
-4. Click the 'Sign In' button
-5. Click on the 'Unified Dashboard for Wireless Management Insights' link
-6. Verify the 'Voice' usage is displayed through graphical design
-7. Verify the breakdown of 'Roaming', 'Overage', and 'In-plan' usages for 'Voice' insight is displayed
-8. Verify the user can drill down on details of both billed and unbilled usages of the Customer's NAG
-9. Verify the 'Voice' usage graph updates when the user selects a different time period from the dropdown</t>
+          <t>1. Click the 'Export' button on the dashboard
+2. Select 'CSV' as the export file type from the dropdown menu
+3. Verify that the exported CSV file includes the Bar Graph's Data, Voice, SMS, and LD Usages
+4. Verify that the exported CSV file includes both Share Plan and individual plans data</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>The user is able to view voice usage through graphical design in the Unified Dashboard for Wireless Management Insights, with breakdown of roaming, overage, and in-plan usages</t>
+          <t>The exported CSV file is downloaded successfully and includes the required data</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>john.doe@company.com, password123</t>
+          <t>Sample dashboard data with Bar Graph's Data, Voice, SMS, and LD Usages</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
@@ -3417,7 +3232,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Unified Dashboard for Wireless Management Insights</t>
+          <t>Export Feature</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3427,12 +3242,12 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Viewing SMS Usage in Unified Dashboard</t>
+          <t>Export Dashboard Details in PDF Format</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view SMS usage through graphical design in the Unified Dashboard for Wireless Management Insights</t>
+          <t>Verify that the user is able to export dashboard details in PDF format</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3445,37 +3260,32 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>The user has a valid login credentials and has access to the Unified Dashboard for Wireless Management Insights</t>
+          <t>User has access to the dashboard and has permission to export data</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter valid username in the 'Email' field, e.g., 'john.doe@company.com'
-3. Enter valid password in the 'Password' field, e.g., 'password123'
-4. Click the 'Sign In' button
-5. Click on the 'Unified Dashboard for Wireless Management Insights' link
-6. Verify the 'SMS' usage is displayed through graphical design
-7. Verify the breakdown of 'Roaming', 'Overage', and 'In-plan' usages for 'SMS' insight is displayed
-8. Verify the user can drill down on details of both billed and unbilled usages of the Customer's NAG
-9. Verify the 'SMS' usage graph updates when the user selects a different time period from the dropdown</t>
+          <t>1. Click the 'Export' button on the dashboard
+2. Select 'PDF' as the export file type from the dropdown menu
+3. Verify that the exported PDF file includes the Bar Graph's Data, Voice, SMS, and LD Usages
+4. Verify that the exported PDF file includes both visual and tabled data</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>The user is able to view SMS usage through graphical design in the Unified Dashboard for Wireless Management Insights, with breakdown of roaming, overage, and in-plan usages</t>
+          <t>The exported PDF file is downloaded successfully and includes the required data</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>john.doe@company.com, password123</t>
+          <t>Sample dashboard data with Bar Graph's Data, Voice, SMS, and LD Usages</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3492,7 +3302,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Unified Dashboard for Wireless Management Insights</t>
+          <t>Export Feature</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -3502,12 +3312,12 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Viewing LD Usage in Unified Dashboard</t>
+          <t>Export Dashboard Details in Invalid Format</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view LD usage through graphical design in the Unified Dashboard for Wireless Management Insights</t>
+          <t>Verify that the user is unable to export dashboard details in an invalid format</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3520,37 +3330,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>The user has a valid login credentials and has access to the Unified Dashboard for Wireless Management Insights</t>
+          <t>User has access to the dashboard and has permission to export data</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter valid username in the 'Email' field, e.g., 'john.doe@company.com'
-3. Enter valid password in the 'Password' field, e.g., 'password123'
-4. Click the 'Sign In' button
-5. Click on the 'Unified Dashboard for Wireless Management Insights' link
-6. Verify the 'LD' usage is displayed through graphical design
-7. Verify the breakdown of 'Roaming', 'Overage', and 'In-plan' usages for 'LD' insight is displayed
-8. Verify the user can drill down on details of both billed and unbilled usages of the Customer's NAG
-9. Verify the 'LD' usage graph updates when the user selects a different time period from the dropdown</t>
+          <t>1. Click the 'Export' button on the dashboard
+2. Select an invalid file type (e.g. 'TXT') from the dropdown menu
+3. Verify that an error message is displayed indicating that the selected file type is not supported</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>The user is able to view LD usage through graphical design in the Unified Dashboard for Wireless Management Insights, with breakdown of roaming, overage, and in-plan usages</t>
+          <t>An error message is displayed indicating that the selected file type is not supported</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>john.doe@company.com, password123</t>
+          <t>Invalid file type (e.g. 'TXT')</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -3562,12 +3366,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>INUTS-014</t>
+          <t>INUTS-015</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Unified Dashboard for Wireless Management Insights</t>
+          <t>NAG Filter</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3577,12 +3381,12 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Invalid Login Credentials</t>
+          <t>Filter Dashboard by NAG</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to access the Unified Dashboard for Wireless Management Insights with invalid login credentials</t>
+          <t>Verify that the user is able to filter the dashboard by NAG</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3602,26 +3406,24 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>The user has invalid login credentials</t>
+          <t>User has access to the dashboard and NAG filter feature</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter invalid username in the 'Email' field, e.g., 'invaliduser@company.com'
-3. Enter invalid password in the 'Password' field, e.g., 'invalidpassword'
-4. Click the 'Sign In' button
-5. Verify an error message is displayed, e.g., 'Invalid username or password'</t>
+          <t>1. Select a NAG from the NAG (Group) Filter dropdown
+2. Verify that the dashboard is updated to show only data relevant to the selected NAG
+3. Verify that the dashboard visualizations, such as Bar Graphs, are updated to reflect the filtered data</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>The user is unable to access the Unified Dashboard for Wireless Management Insights with invalid login credentials</t>
+          <t>The dashboard is filtered to show only data relevant to the selected NAG</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>invaliduser@company.com, invalidpassword</t>
+          <t>NAG (Group) Filter dropdown values</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -3638,7 +3440,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Shopping and Orders Management</t>
+          <t>NAG Filter</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -3648,12 +3450,12 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>View Shopping and Orders Insights</t>
+          <t>Filter Information by NAG</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view their shopping and orders insights, including in-progress, completed, and cancelled orders</t>
+          <t>Verify that the user is able to filter information by NAG</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3666,38 +3468,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>The user must be logged in and have access to the Shopping and Orders Widget</t>
+          <t>User has access to the information and NAG filter feature</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Shopping and Orders Widget
-2. Step 2: Click on the Shopping and Orders tab
-3. Step 3: Verify that the shopping and orders insights are displayed, including in-progress, completed, and cancelled orders
-4. Step 4: Verify that the Latest Orders Table is displayed with the most recent orders
-5. Step 5: Verify that the user can view the details of each order by clicking on the order
-6. Step 6: Verify that the user can view all orders by clicking on the View All Orders link
-7. Step 7: Verify that the user can view the status of each order, including in-progress, completed, and cancelled
-8. Step 8: Verify that the user can view the details of each order, including the order date, order total, and order status
-9. Step 9: Verify that the user can navigate back to the Shopping and Orders Widget by clicking on the Back Button to Drill down table
-10. Step 10: Verify that the user can log out and log back in to verify that the shopping and orders insights are still displayed correctly</t>
+          <t>1. Select a NAG from the NAG (Group) Filter dropdown
+2. Verify that the information is updated to show only data relevant to the selected NAG
+3. Verify that the information details, such as Share Plan vs individual plans, are updated to reflect the filtered data</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>The user is able to view their shopping and orders insights, including in-progress, completed, and cancelled orders, and can navigate through the different orders and view their details</t>
+          <t>The information is filtered to show only data relevant to the selected NAG</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>Test data includes a minimum of 5 orders with different statuses (in-progress, completed, and cancelled) and different order dates and totals</t>
+          <t>NAG (Group) Filter dropdown values</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -3714,7 +3509,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Shopping and Orders Management</t>
+          <t>NAG Filter</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3724,12 +3519,12 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Negative Test - No Orders</t>
+          <t>Invalid NAG Filter Selection</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view a message indicating that there are no orders when there are no orders</t>
+          <t>Verify that the user is unable to filter by an invalid NAG</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3749,27 +3544,24 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>The user must be logged in and have access to the Shopping and Orders Widget, and there must be no orders in the system</t>
+          <t>User has access to the dashboard and NAG filter feature</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Shopping and Orders Widget
-2. Step 2: Click on the Shopping and Orders tab
-3. Step 3: Verify that a message is displayed indicating that there are no orders
-4. Step 4: Verify that the Latest Orders Table is empty
-5. Step 5: Verify that the user can navigate back to the Shopping and Orders Widget by clicking on the Back Button to Drill down table
-6. Step 6: Verify that the user can log out and log back in to verify that the message indicating that there are no orders is still displayed correctly</t>
+          <t>1. Select an invalid NAG from the NAG (Group) Filter dropdown
+2. Verify that an error message is displayed indicating that the NAG is invalid
+3. Verify that the dashboard is not updated to reflect the invalid NAG filter</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>The user is able to view a message indicating that there are no orders when there are no orders</t>
+          <t>An error message is displayed indicating that the NAG is invalid</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Test data includes an empty orders table</t>
+          <t>Invalid NAG (Group) Filter dropdown value</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -3781,12 +3573,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>INUTS-015</t>
+          <t>INUTS-016</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Shopping and Orders Management</t>
+          <t>Quick Links Area</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -3796,12 +3588,12 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Negative Test - Invalid User</t>
+          <t>Quick Links Area Visibility</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to view their shopping and orders insights when they do not have access to the Shopping and Orders Widget</t>
+          <t>Verify that the Quick Links Area is visible to the user</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -3814,34 +3606,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>The user must not have access to the Shopping and Orders Widget</t>
+          <t>User has access to the dashboard</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Shopping and Orders Widget
-2. Step 2: Verify that an error message is displayed indicating that the user does not have access to the Shopping and Orders Widget
-3. Step 3: Verify that the user is unable to view their shopping and orders insights
-4. Step 4: Verify that the user can navigate back to the login page
-5. Step 5: Verify that the user can log in with a different user account that has access to the Shopping and Orders Widget
-6. Step 6: Verify that the user can view their shopping and orders insights with the new user account</t>
+          <t>1. Verify the Quick Links Area is displayed on the dashboard
+2. Verify the Quick Links Area contains links to other Bell tools
+3. Verify the links in the Quick Links Area are clickable</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>The user is unable to view their shopping and orders insights when they do not have access to the Shopping and Orders Widget</t>
+          <t>The Quick Links Area is visible and contains clickable links to other Bell tools</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>Test data includes a user account that does not have access to the Shopping and Orders Widget</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
@@ -3858,7 +3647,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>NAG Favoriting</t>
+          <t>Quick Links Area</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3868,12 +3657,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Favoriting a NAG</t>
+          <t>Quick Links Area Link Functionality</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to favorite a specific NAG</t>
+          <t>Verify that the links in the Quick Links Area redirect to the correct pages</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3886,41 +3675,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>The user must be logged in to My Dashboard with a valid username and password, and have at least one NAG available</t>
+          <t>User has access to the dashboard and the Quick Links Area</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the My Dashboard page
-2. Step 2: Click on the NAG (Group) Filter dropdown and select a NAG
-3. Step 3: Click on the favorite button next to the selected NAG
-4. Step 4: Verify the NAG is marked as favorite
-5. Step 5: Log out of My Dashboard
-6. Step 6: Log back in to My Dashboard
-7. Step 7: Verify the favorited NAG is shown as default
-8. Step 8: Click on a different NAG and verify it is not marked as favorite
-9. Step 9: Click on the favorite button next to the different NAG
-10. Step 10: Verify the different NAG is marked as favorite
-11. Step 11: Log out of My Dashboard
-12. Step 12: Log back in to My Dashboard
-13. Step 13: Verify the newly favorited NAG is shown as default</t>
+          <t>1. Click on a link in the Quick Links Area
+2. Verify the user is redirected to the correct page
+3. Verify the page contains the expected content</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>The user is able to favorite a specific NAG and it is shown as default when logging in to My Dashboard</t>
+          <t>The user is redirected to the correct page and the page contains the expected content</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Valid username: 'john.doe@company.com', valid password: 'password123', NAG name: 'NAG-001'</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -3937,7 +3716,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>NAG Favoriting</t>
+          <t>Quick Links Area</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -3947,12 +3726,12 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Viewing favorited NAG</t>
+          <t>Quick Links Area Error Handling</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view the favorited NAG</t>
+          <t>Verify that the Quick Links Area handles errors correctly</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3965,36 +3744,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>The user must be logged in to My Dashboard with a valid username and password, and have at least one favorited NAG</t>
+          <t>User has access to the dashboard and the Quick Links Area</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the My Dashboard page
-2. Step 2: Verify the favorited NAG is shown as default
-3. Step 3: Click on the favorited NAG
-4. Step 4: Verify the NAG details are displayed
-5. Step 5: Verify the favorite button next to the NAG is highlighted
-6. Step 6: Click on a different NAG
-7. Step 7: Verify the different NAG details are displayed
-8. Step 8: Verify the favorite button next to the different NAG is not highlighted</t>
+          <t>1. Simulate a network error while clicking on a link in the Quick Links Area
+2. Verify an error message is displayed to the user
+3. Verify the error message contains instructions on how to resolve the issue</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>The user is able to view the favorited NAG and its details</t>
+          <t>An error message is displayed to the user with instructions on how to resolve the issue</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>Valid username: 'john.doe@company.com', valid password: 'password123', favorited NAG name: 'NAG-001'</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
@@ -4006,12 +3780,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>INUTS-016</t>
+          <t>INUTS-017</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>NAG Favoriting</t>
+          <t>Bill Cycle Information Display</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4021,12 +3795,12 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Favoriting multiple NAGs</t>
+          <t>Verify Bill Cycle Information Display</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to favorite multiple NAGs</t>
+          <t>Verify that the user is able to view their billing cycle information</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -4039,38 +3813,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>The user must be logged in to My Dashboard with a valid username and password, and have at least two NAGs available</t>
+          <t>User has mydashboard-view or mydashboard-manage permissions</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the My Dashboard page
-2. Step 2: Click on the NAG (Group) Filter dropdown and select a NAG
-3. Step 3: Click on the favorite button next to the selected NAG
-4. Step 4: Verify the NAG is marked as favorite
-5. Step 5: Click on a different NAG
-6. Step 6: Click on the favorite button next to the different NAG
-7. Step 7: Verify the different NAG is marked as favorite
-8. Step 8: Log out of My Dashboard
-9. Step 9: Log back in to My Dashboard
-10. Step 10: Verify both favorited NAGs are shown as default</t>
+          <t>1. Verify the Bill Cycle Information section is displayed
+2. Verify the Open date field displays the start of the bill cycle
+3. Verify the Close date field displays the end of the bill cycle</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>The user is able to favorite multiple NAGs and they are shown as default when logging in to My Dashboard</t>
+          <t>The user can view their billing cycle information, including Open date and Close date</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Valid username: 'john.doe@company.com', valid password: 'password123', NAG names: 'NAG-001', 'NAG-002'</t>
+          <t>Sample bill cycle data with Open date and Close date</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4082,12 +3849,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>INUTS-016</t>
+          <t>INUTS-017</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>NAG Favoriting</t>
+          <t>Bill Cycle Information Display</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -4097,12 +3864,12 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Unfavoriting a NAG</t>
+          <t>Verify Bill Cycle Information Display for Unbilled Usage</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to unfavorite a NAG</t>
+          <t>Verify that the user is able to view their unbilled usage bill cycle information</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -4115,36 +3882,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>The user must be logged in to My Dashboard with a valid username and password, and have at least one favorited NAG</t>
+          <t>User has mydashboard-view or mydashboard-manage permissions and has unbilled usage</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the My Dashboard page
-2. Step 2: Verify the favorited NAG is shown as default
-3. Step 3: Click on the favorited NAG
-4. Step 4: Click on the favorite button next to the NAG
-5. Step 5: Verify the NAG is no longer marked as favorite
-6. Step 6: Log out of My Dashboard
-7. Step 7: Log back in to My Dashboard
-8. Step 8: Verify the NAG is no longer shown as default</t>
+          <t>1. Verify the Unbilled usage section is displayed
+2. Verify the Start of bill cycle to login period is displayed as the unbilled usage period
+3. Verify the Previous month(s) capture of customer's billed usage is displayed</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>The user is able to unfavorite a NAG and it is no longer shown as default when logging in to My Dashboard</t>
+          <t>The user can view their unbilled usage bill cycle information</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>Valid username: 'john.doe@company.com', valid password: 'password123', favorited NAG name: 'NAG-001'</t>
+          <t>Sample unbilled usage data</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
@@ -4161,7 +3923,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Usage and Metric Visualization</t>
+          <t>Bill Cycle Information Display</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4171,12 +3933,12 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Viewing Metric Tiles</t>
+          <t>Verify Bill Cycle Information Display for User without Permissions</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view metric tiles and see accurate data</t>
+          <t>Verify that the user without permissions cannot view their bill cycle information</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -4189,39 +3951,30 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>The user must be logged in and have access to the Usage and Metric Visualization feature</t>
+          <t>User does not have mydashboard-view or mydashboard-manage permissions</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Usage and Metric Visualization page
-2. Step 2: Click on the Metric Tiles section
-3. Step 3: Verify that the metric tiles display accurate data, including Data Usage, Voice, SMS, and LD Usages
-4. Step 4: Interact with the metric tiles by hovering over or clicking on them
-5. Step 5: Verify that the metric tiles update in real-time and display the correct information
-6. Step 6: Test with different types of data, such as shared plans and individual plans
-7. Step 7: Verify that the metric tiles display the correct data for each type of plan
-8. Step 8: Test with different time periods, such as daily, weekly, or monthly
-9. Step 9: Verify that the metric tiles display the correct data for each time period
-10. Step 10: Click on the Back Button to return to the previous page
-11. Step 11: Verify that the page returns to the previous state</t>
+          <t>1. Verify the Bill Cycle Information section is not displayed
+2. Verify an error message is displayed indicating the user does not have permissions</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>The user is able to view metric tiles and see accurate data, and the metric tiles update in real-time</t>
+          <t>The user without permissions cannot view their bill cycle information</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Test data includes different types of plans (shared and individual) and different time periods (daily, weekly, monthly)</t>
+          <t>Sample user without permissions</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4233,12 +3986,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>INUTS-017</t>
+          <t>INUTS-018</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Usage and Metric Visualization</t>
+          <t>Redirection to Filtered View</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -4248,12 +4001,12 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Interacting with Usage Summary Tabs</t>
+          <t>Redirection to Filtered View within My Inventory</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to interact with usage summary tabs and see accurate data</t>
+          <t>Verify that the user is redirected to a filtered view within My Inventory when a metric tile is selected</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -4266,39 +4019,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>The user must be logged in and have access to the Usage and Metric Visualization feature</t>
+          <t>User has access to My Inventory and metric tiles are available</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Usage and Metric Visualization page
-2. Step 2: Click on the Usage Summary Tabs section
-3. Step 3: Verify that the usage summary tabs display accurate data, including Data Usage, Voice, SMS, and LD Usages
-4. Step 4: Interact with the usage summary tabs by clicking on them
-5. Step 5: Verify that the usage summary tabs update in real-time and display the correct information
-6. Step 6: Test with different types of data, such as shared plans and individual plans
-7. Step 7: Verify that the usage summary tabs display the correct data for each type of plan
-8. Step 8: Test with different time periods, such as daily, weekly, or monthly
-9. Step 9: Verify that the usage summary tabs display the correct data for each time period
-10. Step 10: Click on the Back Button to return to the previous page
-11. Step 11: Verify that the page returns to the previous state</t>
+          <t>1. Select a metric tile within My Inventory
+2. Verify the system redirects to a filtered view within My Inventory
+3. Verify the filtered view displays relevant data based on the selected metric tile</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>The user is able to interact with usage summary tabs and see accurate data, and the usage summary tabs update in real-time</t>
+          <t>The user is redirected to a filtered view within My Inventory with relevant data</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>Test data includes different types of plans (shared and individual) and different time periods (daily, weekly, monthly)</t>
+          <t>Metric tile selection</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
@@ -4310,12 +4055,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>INUTS-017</t>
+          <t>INUTS-018</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Usage and Metric Visualization</t>
+          <t>Redirection to Filtered View</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4325,12 +4070,12 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Negative Testing - Invalid Input</t>
+          <t>Redirection to Filtered View with Cancelled Subscribers</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to enter invalid input and sees an error message</t>
+          <t>Verify that the user is redirected to a filtered view with cancelled subscribers when the Cancelled Subscribers metric tile is selected</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -4343,36 +4088,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>The user must be logged in and have access to the Usage and Metric Visualization feature</t>
+          <t>User has access to My Inventory and Cancelled Subscribers metric tile is available</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1. Step 1: Navigate to the Usage and Metric Visualization page
-2. Step 2: Enter invalid input, such as a non-numeric value, in the Data Usage field
-3. Step 3: Verify that an error message is displayed
-4. Step 4: Verify that the user is unable to submit the form with invalid input
-5. Step 5: Test with different types of invalid input, such as special characters or empty fields
-6. Step 6: Verify that an error message is displayed for each type of invalid input
-7. Step 7: Click on the Back Button to return to the previous page
-8. Step 8: Verify that the page returns to the previous state</t>
+          <t>1. Select the Cancelled Subscribers metric tile within My Inventory
+2. Verify the system redirects to a filtered view with a list of subscribers filtered to 'Cancelled'
+3. Verify the filtered view displays relevant data for cancelled subscribers</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>The user is unable to enter invalid input and sees an error message</t>
+          <t>The user is redirected to a filtered view with a list of cancelled subscribers</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Test data includes different types of invalid input, such as non-numeric values, special characters, and empty fields</t>
+          <t>Cancelled Subscribers metric tile selection</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -4389,7 +4129,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Customer Dashboard</t>
+          <t>Redirection to Filtered View</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -4399,12 +4139,12 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Login and View Customer Dashboard</t>
+          <t>Redirection to Filtered View with Suspended Subscribers</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is able to view their account and usage information on the Customer Dashboard</t>
+          <t>Verify that the user is redirected to a filtered view with suspended subscribers when the Suspended Subscribers metric tile is selected</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -4417,38 +4157,31 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>The user has a valid username and password, and is a registered customer</t>
+          <t>User has access to My Inventory and Suspended Subscribers metric tile is available</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter 'john.doe@company.com' in the 'Email' field
-3. Enter 'password123' in the 'Password' field
-4. Click the 'Sign In' button
-5. Verify the Customer Dashboard page is displayed
-6. Verify the dashboard displays the customer's account details, including Number of Billing accounts, Active subscribers, Suspended and Cancelled subscribers
-7. Verify the dashboard displays key wireless management insights and actions, including Data, Voice, SMS and LD usages
-8. Verify the user can drill down on details of both billed and unbilled usages of the Customer's NAG
-9. Verify the dashboard displays Shopping and orders insights, including In progress, completed and cancelled orders
-10. Verify the user can access quick links to provide easier opportunities for self-serve management</t>
+          <t>1. Select the Suspended Subscribers metric tile within My Inventory
+2. Verify the system redirects to a filtered view with a list of subscribers filtered to 'Suspended'
+3. Verify the filtered view displays relevant data for suspended subscribers</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>The Customer Dashboard page is displayed with the customer's account and usage information</t>
+          <t>The user is redirected to a filtered view with a list of suspended subscribers</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>john.doe@company.com, password123</t>
+          <t>Suspended Subscribers metric tile selection</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
@@ -4460,12 +4193,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>INUTS-018</t>
+          <t>INUTS-020</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Customer Dashboard</t>
+          <t>Dashboard Navigation</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4475,12 +4208,12 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Invalid Login Credentials</t>
+          <t>Verify Dashboard Navigation for Data Usage</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to access the Customer Dashboard with invalid login credentials</t>
+          <t>Verify that the user is able to navigate through dashboard widgets to show drill-down/toggle scenarios for data usages</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -4500,27 +4233,25 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>The user has an invalid username or password</t>
+          <t>User has access to the dashboard and has a valid billing account</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Enter 'invaliduser@company.com' in the 'Email' field
-3. Enter 'wrongpassword' in the 'Password' field
-4. Click the 'Sign In' button
-5. Verify an error message is displayed indicating that the login credentials are invalid
-6. Verify the user is not able to access the Customer Dashboard</t>
+          <t>1. Click on the Data Usage Type link in the Usage Bar Chart Drilldown
+2. Verify that the Shareplans Detail Table is displayed with listed details, including Billing Account, Plan Name, # of subscribers, Allowance (MB), Used (MB), and Overage (MB)
+3. Verify that the data is sorted based on billing account's alphabetical order
+4. Verify that the data accurately represents correct allowance, used, and overage values in MB</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>An error message is displayed indicating that the login credentials are invalid</t>
+          <t>The Shareplans Detail Table is displayed with accurate data, and the user can navigate back to the standard Usage Bar Chart view using the Back Button</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>invaliduser@company.com, wrongpassword</t>
+          <t>Valid billing account with data usage</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -4532,12 +4263,12 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>INUTS-018</t>
+          <t>INUTS-020</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Customer Dashboard</t>
+          <t>Dashboard Navigation</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -4547,12 +4278,12 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Empty Login Fields</t>
+          <t>Verify Dashboard Navigation for Voice and Long Distance Usage</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Verify that the user is unable to access the Customer Dashboard with empty login fields</t>
+          <t>Verify that the user is able to navigate through dashboard widgets to show drill-down/toggle scenarios for voice and long distance usages</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -4565,32 +4296,34 @@
           <t>E2E</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>The user has not entered any login credentials</t>
+          <t>User has access to the dashboard and has a valid billing account</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>1. Navigate to the Login page
-2. Leave the 'Email' field empty
-3. Leave the 'Password' field empty
-4. Click the 'Sign In' button
-5. Verify an error message is displayed indicating that the login fields are required
-6. Verify the user is not able to access the Customer Dashboard</t>
+          <t>1. Click on the Voice or Long Distance link in the Usage Bar Chart Drilldown
+2. Verify that the Shareplans Detail Table is displayed with listed details, including Billing Account, Plan Name, # of subscribers, Allowance (Minutes), Used (Minutes), and Overage (Minutes)
+3. Verify that the data is sorted based on billing account's alphabetical order
+4. Verify that the data accurately represents correct allowance, used, and overage values in Minutes</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>An error message is displayed indicating that the login fields are required</t>
-        </is>
-      </c>
-      <c r="L55" s="6" t="inlineStr"/>
+          <t>The Shareplans Detail Table is displayed with accurate data, and the user can navigate back to the standard Usage Bar Chart view using the Back Button</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>Valid billing account with voice or long distance usage</t>
+        </is>
+      </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
           <t>Not Executed</t>
@@ -4600,12 +4333,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>INUTS-019</t>
+          <t>INUTS-020</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>NAG (Group) Filter</t>
+          <t>Dashboard Navigation</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4615,12 +4348,12 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Apply NAG Filter</t>
+          <t>Verify Dashboard Navigation for SMS Usage</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Verify that the user is able to filter information by NAG</t>
+          <t>Verify that the user is able to navigate through dashboard widgets to show drill-down/toggle scenarios for SMS usages</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -4640,1816 +4373,28 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>User has access to the dashboard with NAG filter feature</t>
+          <t>User has access to the dashboard and has a valid billing account</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1. Navigate to the dashboard page
-2. Click on the NAG filter dropdown
-3. Select a NAG group from the dropdown options
-4. Verify the display updates to reflect the filtered information
-5. Enter a valid NAG group name in the search field
-6. Verify the display updates to reflect the filtered information
-7. Clear the search field and verify the display updates to reflect all NAG groups
-8. Apply an invalid NAG group filter and verify an error message is displayed
-9. Verify the error message is 'No results found for the selected NAG group'</t>
+          <t>1. Click on the SMS link in the Usage Bar Chart Drilldown
+2. Verify that the Shareplans Detail Table is displayed with listed details, including Billing Account, Plan Name, # of subscribers, Allowance (# of Text Messages), Used (# of Text Messages), and Overage (# of Text Messages)
+3. Verify that the data is sorted based on billing account's alphabetical order
+4. Verify that the data accurately represents correct allowance, used, and overage values in # of Text Messages</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>The display updates to reflect the filtered information</t>
+          <t>The Shareplans Detail Table is displayed with accurate data, and the user can navigate back to the standard Usage Bar Chart view using the Back Button</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>NAG group name: 'Example NAG Group'</t>
+          <t>Valid billing account with SMS usage</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-019</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>NAG (Group) Filter</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>TC-056</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>NAG Filter Real-Time Update</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to see real-time updates when applying the NAG filter</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>User has access to the dashboard with NAG filter feature</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>1. Navigate to the dashboard page
-2. Click on the NAG filter dropdown
-3. Select a NAG group from the dropdown options
-4. Verify the display updates to reflect the filtered information
-5. Make changes to the NAG group data
-6. Verify the display updates in real-time to reflect the changes
-7. Verify the updated information is accurate and consistent</t>
-        </is>
-      </c>
-      <c r="K57" s="6" t="inlineStr">
-        <is>
-          <t>The display updates in real-time to reflect the changes</t>
-        </is>
-      </c>
-      <c r="L57" s="6" t="inlineStr">
-        <is>
-          <t>NAG group name: 'Example NAG Group'</t>
-        </is>
-      </c>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-019</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>NAG (Group) Filter</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>TC-057</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>NAG Filter Edge Case</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to apply the NAG filter with edge case scenarios</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>User has access to the dashboard with NAG filter feature</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>1. Navigate to the dashboard page
-2. Click on the NAG filter dropdown
-3. Select a NAG group with a large amount of data from the dropdown options
-4. Verify the display updates to reflect the filtered information
-5. Verify the display does not timeout or become unresponsive
-6. Apply a NAG filter with special characters and verify the display updates correctly
-7. Verify the display does not display any error messages</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>The display updates correctly and does not display any error messages</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>NAG group name: 'Example NAG Group with Special Characters'</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-020</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>Latest Orders Table</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>TC-058</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>View Latest Orders</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to view their latest orders</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>The user must be logged in and have at least one order in their history</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the Latest Orders Table
-2. Step 2: Verify the Latest Orders Table is displayed with the correct orders
-3. Step 3: Verify the table has columns for Order ID, Date, and Status Badge
-4. Step 4: Verify the user can view their latest orders in the table
-5. Step 5: Verify the user can see the Order ID, Date, and Status Badge for each order
-6. Step 6: Verify the user can navigate to the View All Orders link from the Latest Orders Table
-7. Step 7: Verify the user is redirected to the View All Orders page when clicking the View All Orders link
-8. Step 8: Verify the user can return to the Latest Orders Table from the View All Orders page
-9. Step 9: Verify the Latest Orders Table is updated with the latest orders after returning from the View All Orders page
-10. Step 10: Verify the user can view their latest orders in the table after updating
-11. Step 11: Verify the table still has columns for Order ID, Date, and Status Badge after updating
-12. Step 12: Verify the user can log out and log back in and still view their latest orders
-13. Step 13: Verify the Latest Orders Table is still displayed with the correct orders after logging back in</t>
-        </is>
-      </c>
-      <c r="K59" s="6" t="inlineStr">
-        <is>
-          <t>The user is able to view their latest orders in the Latest Orders Table with the correct columns and data</t>
-        </is>
-      </c>
-      <c r="L59" s="6" t="inlineStr">
-        <is>
-          <t>Test data: Order ID, Date, and Status Badge for each order</t>
-        </is>
-      </c>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-020</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Latest Orders Table</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>TC-059</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>View Latest Orders with No Orders</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to view a message when they have no orders</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>The user must be logged in and have no orders in their history</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the Latest Orders Table
-2. Step 2: Verify the Latest Orders Table is displayed with a message indicating no orders
-3. Step 3: Verify the message is clear and concise
-4. Step 4: Verify the user can navigate to the View All Orders link from the Latest Orders Table
-5. Step 5: Verify the user is redirected to the View All Orders page when clicking the View All Orders link
-6. Step 6: Verify the user can return to the Latest Orders Table from the View All Orders page
-7. Step 7: Verify the Latest Orders Table is still displayed with the message indicating no orders
-8. Step 8: Verify the user can log out and log back in and still view the message
-9. Step 9: Verify the Latest Orders Table is still displayed with the message indicating no orders after logging back in</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>The user is able to view a message indicating no orders in the Latest Orders Table</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>Test data: No orders in the user's history</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-020</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>Latest Orders Table</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>TC-060</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>View Latest Orders with Invalid Data</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to view an error message when the data is invalid</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>The user must be logged in and have invalid data in their orders</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the Latest Orders Table
-2. Step 2: Verify the Latest Orders Table is displayed with an error message
-3. Step 3: Verify the error message is clear and concise
-4. Step 4: Verify the user can navigate to the View All Orders link from the Latest Orders Table
-5. Step 5: Verify the user is redirected to the View All Orders page when clicking the View All Orders link
-6. Step 6: Verify the user can return to the Latest Orders Table from the View All Orders page
-7. Step 7: Verify the Latest Orders Table is still displayed with the error message
-8. Step 8: Verify the user can log out and log back in and still view the error message
-9. Step 9: Verify the Latest Orders Table is still displayed with the error message after logging back in</t>
-        </is>
-      </c>
-      <c r="K61" s="6" t="inlineStr">
-        <is>
-          <t>The user is able to view an error message in the Latest Orders Table</t>
-        </is>
-      </c>
-      <c r="L61" s="6" t="inlineStr">
-        <is>
-          <t>Test data: Invalid data in the user's orders</t>
-        </is>
-      </c>
-      <c r="M61" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-021</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Permissions - Dashboard View</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>TC-061</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Viewing Permissions on the Dashboard</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to view permissions on the dashboard</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>Existing base of customers is available, user has the required role and permissions to view the dashboard</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the dashboard
-2. Step 2: Click on the 'Permissions' section
-3. Step 3: Verify that the permissions are displayed on the dashboard
-4. Step 4: Verify that the permissions are correctly aligned with the existing base of customers
-5. Step 5: Attempt to capture new permissions
-6. Step 6: Verify that new permissions are captured successfully
-7. Step 7: Verify that the new permissions are displayed on the dashboard
-8. Step 8: Attempt to view permissions with an empty dataset
-9. Step 9: Verify that the dashboard handles the empty dataset correctly
-10. Step 10: Log out of the dashboard
-11. Step 11: Log back in with a different user role
-12. Step 12: Verify that the permissions are not visible to the user without the required role
-13. Step 13: Log out of the dashboard
-14. Step 14: Log back in with the original user role
-15. Step 15: Verify that the permissions are still visible on the dashboard</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>The user is able to view permissions on the dashboard, and new permissions are captured successfully</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>Existing base of customers, new permissions data</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-021</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>Permissions - Dashboard View</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>TC-062</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Viewing Permissions on the Dashboard with Invalid Input</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is unable to view permissions on the dashboard with invalid input</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>Existing base of customers is available, user has the required role and permissions to view the dashboard</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the dashboard
-2. Step 2: Enter invalid input in the 'Permissions' section
-3. Step 3: Verify that an error message is displayed
-4. Step 4: Verify that the permissions are not displayed on the dashboard
-5. Step 5: Attempt to capture new permissions with invalid input
-6. Step 6: Verify that an error message is displayed
-7. Step 7: Verify that new permissions are not captured
-8. Step 8: Log out of the dashboard
-9. Step 9: Log back in with the original user role
-10. Step 10: Verify that the permissions are still visible on the dashboard</t>
-        </is>
-      </c>
-      <c r="K63" s="6" t="inlineStr">
-        <is>
-          <t>The user is unable to view permissions on the dashboard with invalid input, and an error message is displayed</t>
-        </is>
-      </c>
-      <c r="L63" s="6" t="inlineStr">
-        <is>
-          <t>Invalid input data</t>
-        </is>
-      </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-021</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Permissions - Dashboard View</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>TC-063</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Viewing Permissions on the Dashboard with Missing Required Field</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is unable to view permissions on the dashboard with a missing required field</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H64" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>Existing base of customers is available, user has the required role and permissions to view the dashboard</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the dashboard
-2. Step 2: Leave a required field blank in the 'Permissions' section
-3. Step 3: Verify that a validation error message is displayed
-4. Step 4: Verify that the permissions are not displayed on the dashboard
-5. Step 5: Attempt to capture new permissions with a missing required field
-6. Step 6: Verify that a validation error message is displayed
-7. Step 7: Verify that new permissions are not captured
-8. Step 8: Log out of the dashboard
-9. Step 9: Log back in with the original user role
-10. Step 10: Verify that the permissions are still visible on the dashboard</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>The user is unable to view permissions on the dashboard with a missing required field, and a validation error message is displayed</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>Missing required field data</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-022</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>SSC Link Creation</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>TC-064</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Create SSC Link</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to create an SSC link</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>The user has the required permissions to create SSC links and the SSC Development team is available to provide SSC links to the Analance team</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the SSC Link Creation page
-2. Step 2: Enter a valid SSC link name in the 'SSC Link Name' field
-3. Step 3: Enter a valid SSC link description in the 'SSC Link Description' field
-4. Step 4: Click the 'Create SSC Link' button
-5. Step 5: Verify that the SSC link is created successfully and the 'SSC Link Created Successfully' message is displayed
-6. Step 6: Enter an empty SSC link name in the 'SSC Link Name' field and click the 'Create SSC Link' button to test for invalid input
-7. Step 7: Verify that an error message is displayed indicating that the SSC link name is required
-8. Step 8: Navigate back to the SSC Link Creation page and verify that the state is reset</t>
-        </is>
-      </c>
-      <c r="K65" s="6" t="inlineStr">
-        <is>
-          <t>The SSC link is created successfully and the 'SSC Link Created Successfully' message is displayed</t>
-        </is>
-      </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>SSC link name: 'Test SSC Link', SSC link description: 'This is a test SSC link'</t>
-        </is>
-      </c>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-022</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>SSC Link Creation</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>TC-065</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Provide SSC Link to Analance Team</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to provide the created SSC link to the Analance team</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>The user has the required permissions to create SSC links and the SSC Development team is available to provide SSC links to the Analance team</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the SSC Link Creation page
-2. Step 2: Enter a valid SSC link name in the 'SSC Link Name' field
-3. Step 3: Enter a valid SSC link description in the 'SSC Link Description' field
-4. Step 4: Click the 'Create SSC Link' button
-5. Step 5: Verify that the SSC link is created successfully and the 'SSC Link Created Successfully' message is displayed
-6. Step 6: Click the 'Share SSC Link' button
-7. Step 7: Select the Analance team from the 'Share With' dropdown
-8. Step 8: Verify that the SSC link is shared successfully with the Analance team and a confirmation message is displayed</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>The SSC link is shared successfully with the Analance team and a confirmation message is displayed</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>SSC link name: 'Test SSC Link', SSC link description: 'This is a test SSC link', Analance team: 'Analance Team'</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-023</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>PTW Self Serve CS</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>TC-066</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Navigating through the PTW Self Serve CS sequence</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to navigate through the PTW Self Serve CS sequence and view the interactions between different systems and components</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>The user has the necessary permissions to access the PTW Self Serve CS sequence</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the Play to Win Solutions Page
-2. Step 2: Click on the link to access the PTW Self Serve CS sequence
-3. Step 3: Verify that the PTW Self Serve CS sequence is displayed
-4. Step 4: Verify that the sequence includes all necessary interactions between the customer, BBSSC, ESIDE, NM1, BCIM, Kafka, IDD, and Analance
-5. Step 5: Drill down on details of both billed and unbilled usages of the Customer's NAG
-6. Step 6: Verify that the breakdown of Roaming, Overage, and In-plan usages for each insight is displayed
-7. Step 7: Verify that the Shopping and orders insights are displayed, including In progress, completed, and cancelled
-8. Step 8: Verify that the quick links area provides customers with easier access to other Bell tools
-9. Step 9: Verify that the user can view summarized tiles regarding account details, including Number of Billing accounts, Active subscribers, Suspended and Cancelled subscribers
-10. Step 10: Verify that the user can view key wireless management insights and actions in a single dashboard
-11. Step 11: Verify that the user can view Data, Voice, SMS, and LD usages through graphical design
-12. Step 12: Verify that the user can proactively manage self-serve their overage</t>
-        </is>
-      </c>
-      <c r="K67" s="6" t="inlineStr">
-        <is>
-          <t>The user is able to navigate through the PTW Self Serve CS sequence and view the interactions between different systems and components</t>
-        </is>
-      </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>Test data includes a valid user account with the necessary permissions to access the PTW Self Serve CS sequence</t>
-        </is>
-      </c>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-023</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>PTW Self Serve CS</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>TC-067</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Invalid access to PTW Self Serve CS sequence</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is unable to access the PTW Self Serve CS sequence without the necessary permissions</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>The user does not have the necessary permissions to access the PTW Self Serve CS sequence</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the Play to Win Solutions Page
-2. Step 2: Attempt to access the PTW Self Serve CS sequence without the necessary permissions
-3. Step 3: Verify that an error message is displayed indicating that the user does not have the necessary permissions
-4. Step 4: Verify that the user is unable to view the PTW Self Serve CS sequence</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>The user is unable to access the PTW Self Serve CS sequence without the necessary permissions</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>Test data includes a valid user account without the necessary permissions to access the PTW Self Serve CS sequence</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-024</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>Usage Details Drilldown</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>TC-068</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Drilldown on Billed Usage</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to drill down on billed usage details</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>The user has a valid login credentials and has at least one billed usage account</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the Usage Bar Chart Drilldown View
-2. Step 2: Select a billed usage account from the list of available accounts
-3. Step 3: Click on the drilldown button for the selected billed usage account
-4. Step 4: Verify that the detailed usage data is displayed, including allowance, used data, and overage
-5. Step 5: Verify that the data is accurately represented in numerical values in MB for Data, Minutes for Voice and Long Distance, and # of Text Messages for Text Messaging
-6. Step 6: Verify that the Subscriber # is a selectable link and brings the customer to the preexisting My Inventory page - Individual Subscriber Page
-7. Step 7: Verify that the Billing account is a selectable link and brings the customer to the preexisting my inventory section to display Billing account usage details page
-8. Step 8: Click on the Back Button and verify that the user is brought back to the standard Usage Bar Chart Drilldown View</t>
-        </is>
-      </c>
-      <c r="K69" s="6" t="inlineStr">
-        <is>
-          <t>The user is able to drill down on billed usage details and view the detailed usage data</t>
-        </is>
-      </c>
-      <c r="L69" s="6" t="inlineStr">
-        <is>
-          <t>Billed usage account with valid data</t>
-        </is>
-      </c>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-024</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Usage Details Drilldown</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>TC-069</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Drilldown on Unbilled Usage</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to drill down on unbilled usage details</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>The user has a valid login credentials and has at least one unbilled usage account</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the Usage Bar Chart Drilldown View
-2. Step 2: Select an unbilled usage account from the list of available accounts
-3. Step 3: Click on the drilldown button for the selected unbilled usage account
-4. Step 4: Verify that the detailed usage data is displayed, including allowance, used data, and overage
-5. Step 5: Verify that the data is accurately represented in numerical values in MB for Data, Minutes for Voice and Long Distance, and # of Text Messages for Text Messaging
-6. Step 6: Verify that the Subscriber # is a selectable link and brings the customer to the preexisting My Inventory page - Individual Subscriber Page
-7. Step 7: Verify that the Billing account is a selectable link and brings the customer to the preexisting my inventory section to display Billing account usage details page
-8. Step 8: Click on the Back Button and verify that the user is brought back to the standard Usage Bar Chart Drilldown View</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>The user is able to drill down on unbilled usage details and view the detailed usage data</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>Unbilled usage account with valid data</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-024</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>Usage Details Drilldown</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>TC-070</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>Drilldown on Billed Usage with No Data</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to drill down on billed usage details with no data</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>The user has a valid login credentials and has at least one billed usage account with no data</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the Usage Bar Chart Drilldown View
-2. Step 2: Select a billed usage account with no data from the list of available accounts
-3. Step 3: Click on the drilldown button for the selected billed usage account
-4. Step 4: Verify that a message is displayed indicating that there is no data available
-5. Step 5: Verify that the user is able to navigate back to the standard Usage Bar Chart Drilldown View</t>
-        </is>
-      </c>
-      <c r="K71" s="6" t="inlineStr">
-        <is>
-          <t>The user is able to drill down on billed usage details with no data and view a message indicating that there is no data available</t>
-        </is>
-      </c>
-      <c r="L71" s="6" t="inlineStr">
-        <is>
-          <t>Billed usage account with no data</t>
-        </is>
-      </c>
-      <c r="M71" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-024</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Usage Details Drilldown</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>TC-071</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Drilldown on Unbilled Usage with No Data</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to drill down on unbilled usage details with no data</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>The user has a valid login credentials and has at least one unbilled usage account with no data</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the Usage Bar Chart Drilldown View
-2. Step 2: Select an unbilled usage account with no data from the list of available accounts
-3. Step 3: Click on the drilldown button for the selected unbilled usage account
-4. Step 4: Verify that a message is displayed indicating that there is no data available
-5. Step 5: Verify that the user is able to navigate back to the standard Usage Bar Chart Drilldown View</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>The user is able to drill down on unbilled usage details with no data and view a message indicating that there is no data available</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>Unbilled usage account with no data</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-025</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>Link to Manage My Access</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>TC-072</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>Link to Manage My Access</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to manage their access by clicking on the link to manage my access</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>The user must be logged in to the dashboard</t>
-        </is>
-      </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the dashboard
-2. Step 2: Locate the link to manage my access on the dashboard
-3. Step 3: Click on the link to manage my access
-4. Step 4: Verify the user is taken to the manage my access page
-5. Step 5: Verify the manage my access page displays the user's account information
-6. Step 6: Verify the user can update their account information on the manage my access page
-7. Step 7: Enter updated account information and save changes
-8. Step 8: Verify the updated account information is reflected on the manage my access page</t>
-        </is>
-      </c>
-      <c r="K73" s="6" t="inlineStr">
-        <is>
-          <t>The user is able to manage their access by clicking on the link to manage my access and updating their account information</t>
-        </is>
-      </c>
-      <c r="L73" s="6" t="inlineStr">
-        <is>
-          <t>Valid user credentials and updated account information</t>
-        </is>
-      </c>
-      <c r="M73" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-025</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Link to Manage My Access</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>TC-073</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Invalid Access to Manage My Access</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is unable to access the manage my access page without proper permissions</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>The user must not have permissions to access the manage my access page</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the dashboard as a user without permissions to access the manage my access page
-2. Step 2: Attempt to click on the link to manage my access
-3. Step 3: Verify an error message is displayed indicating the user does not have permission to access the manage my access page
-4. Step 4: Verify the user is not taken to the manage my access page</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>The user is unable to access the manage my access page without proper permissions</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>Invalid user credentials</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-026</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>UI Widget Creation</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>TC-074</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>Create UI Widget</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to create a UI widget</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>The user has the necessary permissions to create UI widgets and is a member of the Analance team</t>
-        </is>
-      </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the UI Widget Creation page
-2. Step 2: Click the 'Create UI Widget' button
-3. Step 3: Enter 'Test UI Widget' in the 'UI Widget Name' field
-4. Step 4: Select 'Active' from the 'UI Widget Status' dropdown
-5. Step 5: Click the 'Save UI Widget' button
-6. Step 6: Verify the 'UI Widget Created Successfully' message is displayed
-7. Step 7: Verify the created UI widget is listed on the UI Widget Creation page
-8. Step 8: Enter an empty string in the 'UI Widget Name' field and click the 'Save UI Widget' button
-9. Step 9: Verify the 'UI Widget Name is required' error message is displayed
-10. Step 10: Enter a UI widget name with more than 50 characters and click the 'Save UI Widget' button
-11. Step 11: Verify the 'UI Widget Name must be less than 50 characters' error message is displayed
-12. Step 12: Logout and verify that the created UI widget is still listed on the UI Widget Creation page</t>
-        </is>
-      </c>
-      <c r="K75" s="6" t="inlineStr">
-        <is>
-          <t>The user is able to create a UI widget and it is listed on the UI Widget Creation page</t>
-        </is>
-      </c>
-      <c r="L75" s="6" t="inlineStr">
-        <is>
-          <t>UI Widget Name: Test UI Widget, UI Widget Status: Active</t>
-        </is>
-      </c>
-      <c r="M75" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-026</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>UI Widget Creation</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>TC-075</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>Create UI Widget with Invalid Input</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is unable to create a UI widget with invalid input</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>The user has the necessary permissions to create UI widgets and is a member of the Analance team</t>
-        </is>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the UI Widget Creation page
-2. Step 2: Click the 'Create UI Widget' button
-3. Step 3: Enter an empty string in the 'UI Widget Name' field
-4. Step 4: Click the 'Save UI Widget' button
-5. Step 5: Verify the 'UI Widget Name is required' error message is displayed
-6. Step 6: Enter a UI widget name with more than 50 characters
-7. Step 7: Click the 'Save UI Widget' button
-8. Step 8: Verify the 'UI Widget Name must be less than 50 characters' error message is displayed
-9. Step 9: Enter a UI widget name with special characters
-10. Step 10: Click the 'Save UI Widget' button
-11. Step 11: Verify the 'UI Widget Name must only contain alphanumeric characters' error message is displayed
-12. Step 12: Logout and verify that no UI widget is created</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>The user is unable to create a UI widget with invalid input</t>
-        </is>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
-        <is>
-          <t>UI Widget Name: , UI Widget Status: Active</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-026</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>UI Widget Creation</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>TC-076</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Create UI Widget without Permissions</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is unable to create a UI widget without the necessary permissions</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>The user does not have the necessary permissions to create UI widgets</t>
-        </is>
-      </c>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the UI Widget Creation page
-2. Step 2: Click the 'Create UI Widget' button
-3. Step 3: Verify the 'Access Denied' error message is displayed
-4. Step 4: Verify that the user is unable to create a UI widget
-5. Step 5: Logout and verify that no UI widget is created</t>
-        </is>
-      </c>
-      <c r="K77" s="6" t="inlineStr">
-        <is>
-          <t>The user is unable to create a UI widget without the necessary permissions</t>
-        </is>
-      </c>
-      <c r="L77" s="6" t="inlineStr"/>
-      <c r="M77" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-027</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>IDR/IDD Billed Data</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>TC-077</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>View IDR/IDD Billed Data</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is able to view IDR/IDD billed data</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>User has the necessary role/permissions to access IDR/IDD billed data</t>
-        </is>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the IDR/IDD Billed Data page
-2. Step 2: Verify the IDR/IDD billed data is displayed
-3. Step 3: Verify the IDR/IDD billed data is accurate
-4. Step 4: Verify the user can view the billed data for a specific billing period
-5. Step 5: Verify the user can view the billed data for a specific IDR/IDD team
-6. Step 6: Enter invalid input in the search field and verify an error message is displayed
-7. Step 7: Leave the search field blank and verify a validation message is displayed
-8. Step 8: Verify the user can navigate back to the previous page
-9. Step 9: Verify the user can log out of the system
-10. Step 10: Verify the system resets to its original state after logout</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>The user is able to view IDR/IDD billed data and verify its accuracy</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>Valid IDR/IDD team name, valid billing period</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>INUTS-027</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>IDR/IDD Billed Data</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>TC-078</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>View IDR/IDD Billed Data with Invalid Input</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>Verify that the user is unable to view IDR/IDD billed data with invalid input</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>User has the necessary role/permissions to access IDR/IDD billed data</t>
-        </is>
-      </c>
-      <c r="J79" s="6" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the IDR/IDD Billed Data page
-2. Step 2: Enter invalid input in the search field
-3. Step 3: Verify an error message is displayed
-4. Step 4: Verify the user cannot view the billed data
-5. Step 5: Verify the user can navigate back to the previous page
-6. Step 6: Verify the user can log out of the system
-7. Step 7: Verify the system resets to its original state after logout</t>
-        </is>
-      </c>
-      <c r="K79" s="6" t="inlineStr">
-        <is>
-          <t>The user is unable to view IDR/IDD billed data with invalid input and an error message is displayed</t>
-        </is>
-      </c>
-      <c r="L79" s="6" t="inlineStr">
-        <is>
-          <t>Invalid IDR/IDD team name, invalid billing period</t>
-        </is>
-      </c>
-      <c r="M79" s="5" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>INUTS-027</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>IDR/IDD Billed Data</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>TC-079</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>View IDR/IDD Billed Data with Missing Required Field</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>Verify that the user is unable to view IDR/IDD billed data with a missing required field</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="H80" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>User has the necessary role/permissions to access IDR/IDD billed data</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>1. Step 1: Navigate to the IDR/IDD Billed Data page
-2. Step 2: Leave the required field blank
-3. Step 3: Verify a validation message is displayed
-4. Step 4: Verify the user cannot view the billed data
-5. Step 5: Verify the user can navigate back to the previous page
-6. Step 6: Verify the user can log out of the system
-7. Step 7: Verify the system resets to its original state after logout</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>The user is unable to view IDR/IDD billed data with a missing required field and a validation message is displayed</t>
-        </is>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>Blank required field</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
